--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486636</v>
+        <v>121486742</v>
       </c>
       <c r="B2" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499244</v>
+        <v>499140</v>
       </c>
       <c r="R2" t="n">
-        <v>6820418</v>
+        <v>6820485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486635</v>
+        <v>121486718</v>
       </c>
       <c r="B3" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499279</v>
+        <v>499079</v>
       </c>
       <c r="R3" t="n">
-        <v>6820470</v>
+        <v>6820344</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486719</v>
+        <v>121486636</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499078</v>
+        <v>499244</v>
       </c>
       <c r="R4" t="n">
-        <v>6820349</v>
+        <v>6820418</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486626</v>
+        <v>121486586</v>
       </c>
       <c r="B5" t="n">
-        <v>97048</v>
+        <v>79222</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499104</v>
+        <v>499101</v>
       </c>
       <c r="R5" t="n">
-        <v>6820567</v>
+        <v>6820489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486720</v>
+        <v>121486651</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499064</v>
+        <v>499244</v>
       </c>
       <c r="R6" t="n">
-        <v>6820411</v>
+        <v>6820418</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486649</v>
+        <v>121486713</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,46 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499099</v>
+        <v>499123</v>
       </c>
       <c r="R7" t="n">
-        <v>6820449</v>
+        <v>6820323</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486591</v>
+        <v>121486626</v>
       </c>
       <c r="B8" t="n">
-        <v>74710</v>
+        <v>97049</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499060</v>
+        <v>499104</v>
       </c>
       <c r="R8" t="n">
-        <v>6820434</v>
+        <v>6820567</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486646</v>
+        <v>121486658</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>78340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,46 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499124</v>
+        <v>499221</v>
       </c>
       <c r="R9" t="n">
-        <v>6820580</v>
+        <v>6820551</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1473,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1509,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486739</v>
+        <v>121486648</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,38 +1503,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499079</v>
+        <v>499087</v>
       </c>
       <c r="R10" t="n">
-        <v>6820445</v>
+        <v>6820462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,6 +1583,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1611,7 +1602,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486729</v>
+        <v>121486738</v>
       </c>
       <c r="B11" t="n">
         <v>78604</v>
@@ -1651,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499121</v>
+        <v>499060</v>
       </c>
       <c r="R11" t="n">
-        <v>6820578</v>
+        <v>6820435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486648</v>
+        <v>121486591</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>74710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,46 +1716,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499087</v>
+        <v>499060</v>
       </c>
       <c r="R12" t="n">
-        <v>6820462</v>
+        <v>6820434</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1788,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1824,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486718</v>
+        <v>121486611</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>79714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1864,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499079</v>
+        <v>499075</v>
       </c>
       <c r="R13" t="n">
-        <v>6820344</v>
+        <v>6820457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486641</v>
+        <v>121486739</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1942,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1966,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499241</v>
+        <v>499079</v>
       </c>
       <c r="R14" t="n">
-        <v>6820619</v>
+        <v>6820445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486728</v>
+        <v>121486637</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2044,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499103</v>
+        <v>499221</v>
       </c>
       <c r="R15" t="n">
-        <v>6820567</v>
+        <v>6820551</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,7 +2112,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486721</v>
+        <v>121486745</v>
       </c>
       <c r="B16" t="n">
         <v>78604</v>
@@ -2170,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499066</v>
+        <v>499219</v>
       </c>
       <c r="R16" t="n">
-        <v>6820416</v>
+        <v>6820563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486652</v>
+        <v>121486740</v>
       </c>
       <c r="B17" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2248,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2272,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499247</v>
+        <v>499119</v>
       </c>
       <c r="R17" t="n">
-        <v>6820414</v>
+        <v>6820450</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,7 +2316,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486743</v>
+        <v>121486712</v>
       </c>
       <c r="B18" t="n">
         <v>78604</v>
@@ -2374,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499204</v>
+        <v>499123</v>
       </c>
       <c r="R18" t="n">
-        <v>6820546</v>
+        <v>6820315</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486742</v>
+        <v>121486641</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2452,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499140</v>
+        <v>499241</v>
       </c>
       <c r="R19" t="n">
-        <v>6820485</v>
+        <v>6820619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486629</v>
+        <v>121486644</v>
       </c>
       <c r="B20" t="n">
-        <v>8432</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2550,36 +2532,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2590,7 +2571,7 @@
         <v>499088</v>
       </c>
       <c r="R20" t="n">
-        <v>6820469</v>
+        <v>6820326</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2650,10 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486703</v>
+        <v>121486629</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>8432</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2662,38 +2643,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499321</v>
+        <v>499088</v>
       </c>
       <c r="R21" t="n">
-        <v>6820523</v>
+        <v>6820469</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,6 +2724,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2752,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486717</v>
+        <v>121486612</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>79714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2764,25 +2755,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2792,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499081</v>
+        <v>499163</v>
       </c>
       <c r="R22" t="n">
-        <v>6820327</v>
+        <v>6820511</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2854,7 +2845,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486658</v>
+        <v>121486653</v>
       </c>
       <c r="B23" t="n">
         <v>78340</v>
@@ -2894,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499221</v>
+        <v>499063</v>
       </c>
       <c r="R23" t="n">
-        <v>6820551</v>
+        <v>6820418</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2956,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486738</v>
+        <v>121486646</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,38 +2959,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499060</v>
+        <v>499124</v>
       </c>
       <c r="R24" t="n">
-        <v>6820435</v>
+        <v>6820580</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3040,6 +3039,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486712</v>
+        <v>121486643</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>80561</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499123</v>
+        <v>499159</v>
       </c>
       <c r="R25" t="n">
-        <v>6820315</v>
+        <v>6820599</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486623</v>
+        <v>121486719</v>
       </c>
       <c r="B26" t="n">
-        <v>79686</v>
+        <v>78604</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3176,21 +3176,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499112</v>
+        <v>499078</v>
       </c>
       <c r="R26" t="n">
-        <v>6820448</v>
+        <v>6820349</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486744</v>
+        <v>121486710</v>
       </c>
       <c r="B27" t="n">
         <v>78604</v>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499210</v>
+        <v>499134</v>
       </c>
       <c r="R27" t="n">
-        <v>6820548</v>
+        <v>6820297</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486740</v>
+        <v>121486748</v>
       </c>
       <c r="B28" t="n">
         <v>78604</v>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499119</v>
+        <v>499224</v>
       </c>
       <c r="R28" t="n">
-        <v>6820450</v>
+        <v>6820584</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486612</v>
+        <v>121486635</v>
       </c>
       <c r="B29" t="n">
-        <v>79714</v>
+        <v>78341</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3478,25 +3478,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499163</v>
+        <v>499279</v>
       </c>
       <c r="R29" t="n">
-        <v>6820511</v>
+        <v>6820470</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486745</v>
+        <v>121486720</v>
       </c>
       <c r="B30" t="n">
         <v>78604</v>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499219</v>
+        <v>499064</v>
       </c>
       <c r="R30" t="n">
-        <v>6820563</v>
+        <v>6820411</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486748</v>
+        <v>121486714</v>
       </c>
       <c r="B31" t="n">
         <v>78604</v>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499224</v>
+        <v>499120</v>
       </c>
       <c r="R31" t="n">
-        <v>6820584</v>
+        <v>6820327</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486731</v>
+        <v>121486652</v>
       </c>
       <c r="B32" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3788,21 +3788,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499150</v>
+        <v>499247</v>
       </c>
       <c r="R32" t="n">
-        <v>6820595</v>
+        <v>6820414</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3874,10 +3874,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486653</v>
+        <v>121486728</v>
       </c>
       <c r="B33" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3890,21 +3890,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499063</v>
+        <v>499103</v>
       </c>
       <c r="R33" t="n">
-        <v>6820418</v>
+        <v>6820567</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486611</v>
+        <v>121486654</v>
       </c>
       <c r="B34" t="n">
-        <v>79714</v>
+        <v>78340</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3988,25 +3988,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499075</v>
+        <v>499174</v>
       </c>
       <c r="R34" t="n">
-        <v>6820457</v>
+        <v>6820509</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4078,10 +4078,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486651</v>
+        <v>121486640</v>
       </c>
       <c r="B35" t="n">
-        <v>78340</v>
+        <v>79685</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4094,21 +4094,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4118,10 +4118,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499244</v>
+        <v>499110</v>
       </c>
       <c r="R35" t="n">
-        <v>6820418</v>
+        <v>6820446</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486586</v>
+        <v>121486711</v>
       </c>
       <c r="B36" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499101</v>
+        <v>499126</v>
       </c>
       <c r="R36" t="n">
-        <v>6820489</v>
+        <v>6820301</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486654</v>
+        <v>121486649</v>
       </c>
       <c r="B37" t="n">
-        <v>78340</v>
+        <v>98095</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4294,38 +4294,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499174</v>
+        <v>499099</v>
       </c>
       <c r="R37" t="n">
-        <v>6820509</v>
+        <v>6820449</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4366,6 +4374,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4384,7 +4393,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486711</v>
+        <v>121486731</v>
       </c>
       <c r="B38" t="n">
         <v>78604</v>
@@ -4424,10 +4433,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499126</v>
+        <v>499150</v>
       </c>
       <c r="R38" t="n">
-        <v>6820301</v>
+        <v>6820595</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4486,10 +4495,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486730</v>
+        <v>121486592</v>
       </c>
       <c r="B39" t="n">
-        <v>78604</v>
+        <v>74710</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4502,21 +4511,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4526,10 +4535,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499159</v>
+        <v>499180</v>
       </c>
       <c r="R39" t="n">
-        <v>6820605</v>
+        <v>6820509</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4588,10 +4597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486714</v>
+        <v>121486628</v>
       </c>
       <c r="B40" t="n">
-        <v>78604</v>
+        <v>8432</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4600,38 +4609,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499120</v>
+        <v>499248</v>
       </c>
       <c r="R40" t="n">
-        <v>6820327</v>
+        <v>6820414</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,12 +4684,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4690,10 +4714,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486637</v>
+        <v>121486743</v>
       </c>
       <c r="B41" t="n">
-        <v>78341</v>
+        <v>78604</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4706,21 +4730,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4730,10 +4754,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499221</v>
+        <v>499204</v>
       </c>
       <c r="R41" t="n">
-        <v>6820551</v>
+        <v>6820546</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4792,10 +4816,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486713</v>
+        <v>121486766</v>
       </c>
       <c r="B42" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4808,21 +4832,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4832,10 +4856,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499123</v>
+        <v>499091</v>
       </c>
       <c r="R42" t="n">
-        <v>6820323</v>
+        <v>6820459</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4894,10 +4918,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486640</v>
+        <v>121486744</v>
       </c>
       <c r="B43" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4910,21 +4934,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4934,10 +4958,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499110</v>
+        <v>499210</v>
       </c>
       <c r="R43" t="n">
-        <v>6820446</v>
+        <v>6820548</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4996,10 +5020,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486644</v>
+        <v>121486587</v>
       </c>
       <c r="B44" t="n">
-        <v>98094</v>
+        <v>79222</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5008,46 +5032,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499088</v>
+        <v>499137</v>
       </c>
       <c r="R44" t="n">
-        <v>6820326</v>
+        <v>6820469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5088,7 +5104,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5107,7 +5122,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486710</v>
+        <v>121486715</v>
       </c>
       <c r="B45" t="n">
         <v>78604</v>
@@ -5147,10 +5162,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499134</v>
+        <v>499085</v>
       </c>
       <c r="R45" t="n">
-        <v>6820297</v>
+        <v>6820324</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5209,10 +5224,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486587</v>
+        <v>121486721</v>
       </c>
       <c r="B46" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5225,21 +5240,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5249,10 +5264,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499137</v>
+        <v>499066</v>
       </c>
       <c r="R46" t="n">
-        <v>6820469</v>
+        <v>6820416</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5311,10 +5326,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486592</v>
+        <v>121486703</v>
       </c>
       <c r="B47" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5327,21 +5342,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5351,10 +5366,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499180</v>
+        <v>499321</v>
       </c>
       <c r="R47" t="n">
-        <v>6820509</v>
+        <v>6820523</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5413,7 +5428,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486715</v>
+        <v>121486717</v>
       </c>
       <c r="B48" t="n">
         <v>78604</v>
@@ -5453,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499085</v>
+        <v>499081</v>
       </c>
       <c r="R48" t="n">
-        <v>6820324</v>
+        <v>6820327</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5515,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486628</v>
+        <v>121486623</v>
       </c>
       <c r="B49" t="n">
-        <v>8432</v>
+        <v>79686</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5527,47 +5542,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499248</v>
+        <v>499112</v>
       </c>
       <c r="R49" t="n">
-        <v>6820414</v>
+        <v>6820448</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5602,18 +5608,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486643</v>
+        <v>121486722</v>
       </c>
       <c r="B50" t="n">
-        <v>80561</v>
+        <v>78604</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499159</v>
+        <v>499063</v>
       </c>
       <c r="R50" t="n">
-        <v>6820599</v>
+        <v>6820429</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486766</v>
+        <v>121486729</v>
       </c>
       <c r="B51" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499091</v>
+        <v>499121</v>
       </c>
       <c r="R51" t="n">
-        <v>6820459</v>
+        <v>6820578</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,7 +5836,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486722</v>
+        <v>121486730</v>
       </c>
       <c r="B52" t="n">
         <v>78604</v>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499063</v>
+        <v>499159</v>
       </c>
       <c r="R52" t="n">
-        <v>6820429</v>
+        <v>6820605</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121486742</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486718</v>
+        <v>121486739</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>499079</v>
       </c>
       <c r="R3" t="n">
-        <v>6820344</v>
+        <v>6820445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486636</v>
+        <v>121486587</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499244</v>
+        <v>499137</v>
       </c>
       <c r="R4" t="n">
-        <v>6820418</v>
+        <v>6820469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486586</v>
+        <v>121486703</v>
       </c>
       <c r="B5" t="n">
-        <v>79222</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499101</v>
+        <v>499321</v>
       </c>
       <c r="R5" t="n">
-        <v>6820489</v>
+        <v>6820523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486651</v>
+        <v>121486738</v>
       </c>
       <c r="B6" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499244</v>
+        <v>499060</v>
       </c>
       <c r="R6" t="n">
-        <v>6820418</v>
+        <v>6820435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486713</v>
+        <v>121486714</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499123</v>
+        <v>499120</v>
       </c>
       <c r="R7" t="n">
-        <v>6820323</v>
+        <v>6820327</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486626</v>
+        <v>121486712</v>
       </c>
       <c r="B8" t="n">
-        <v>97049</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499104</v>
+        <v>499123</v>
       </c>
       <c r="R8" t="n">
-        <v>6820567</v>
+        <v>6820315</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486658</v>
+        <v>121486729</v>
       </c>
       <c r="B9" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499221</v>
+        <v>499121</v>
       </c>
       <c r="R9" t="n">
-        <v>6820551</v>
+        <v>6820578</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486648</v>
+        <v>121486721</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,46 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499087</v>
+        <v>499066</v>
       </c>
       <c r="R10" t="n">
-        <v>6820462</v>
+        <v>6820416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,7 +1575,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1602,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486738</v>
+        <v>121486743</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499060</v>
+        <v>499204</v>
       </c>
       <c r="R11" t="n">
-        <v>6820435</v>
+        <v>6820546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486591</v>
+        <v>121486592</v>
       </c>
       <c r="B12" t="n">
-        <v>74710</v>
+        <v>74713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499060</v>
+        <v>499180</v>
       </c>
       <c r="R12" t="n">
-        <v>6820434</v>
+        <v>6820509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486611</v>
+        <v>121486711</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499075</v>
+        <v>499126</v>
       </c>
       <c r="R13" t="n">
-        <v>6820457</v>
+        <v>6820301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486739</v>
+        <v>121486628</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>8435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,38 +1911,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499079</v>
+        <v>499248</v>
       </c>
       <c r="R14" t="n">
-        <v>6820445</v>
+        <v>6820414</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,12 +1986,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486637</v>
+        <v>121486658</v>
       </c>
       <c r="B15" t="n">
-        <v>78341</v>
+        <v>78343</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486745</v>
+        <v>121486713</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499219</v>
+        <v>499123</v>
       </c>
       <c r="R16" t="n">
-        <v>6820563</v>
+        <v>6820323</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486740</v>
+        <v>121486710</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2254,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499119</v>
+        <v>499134</v>
       </c>
       <c r="R17" t="n">
-        <v>6820450</v>
+        <v>6820297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486712</v>
+        <v>121486745</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2356,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499123</v>
+        <v>499219</v>
       </c>
       <c r="R18" t="n">
-        <v>6820315</v>
+        <v>6820563</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486641</v>
+        <v>121486744</v>
       </c>
       <c r="B19" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499241</v>
+        <v>499210</v>
       </c>
       <c r="R19" t="n">
-        <v>6820619</v>
+        <v>6820548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486644</v>
+        <v>121486654</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
+        <v>78343</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,46 +2538,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499088</v>
+        <v>499174</v>
       </c>
       <c r="R20" t="n">
-        <v>6820326</v>
+        <v>6820509</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,7 +2610,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2631,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486629</v>
+        <v>121486728</v>
       </c>
       <c r="B21" t="n">
-        <v>8432</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,47 +2640,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499088</v>
+        <v>499103</v>
       </c>
       <c r="R21" t="n">
-        <v>6820469</v>
+        <v>6820567</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,7 +2712,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2743,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486612</v>
+        <v>121486646</v>
       </c>
       <c r="B22" t="n">
-        <v>79714</v>
+        <v>98098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,38 +2742,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499163</v>
+        <v>499124</v>
       </c>
       <c r="R22" t="n">
-        <v>6820511</v>
+        <v>6820580</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,6 +2822,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2845,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486653</v>
+        <v>121486748</v>
       </c>
       <c r="B23" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2861,21 +2857,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499063</v>
+        <v>499224</v>
       </c>
       <c r="R23" t="n">
-        <v>6820418</v>
+        <v>6820584</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486646</v>
+        <v>121486722</v>
       </c>
       <c r="B24" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,46 +2955,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499124</v>
+        <v>499063</v>
       </c>
       <c r="R24" t="n">
-        <v>6820580</v>
+        <v>6820429</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3027,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3058,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486643</v>
+        <v>121486720</v>
       </c>
       <c r="B25" t="n">
-        <v>80561</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3074,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3098,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499159</v>
+        <v>499064</v>
       </c>
       <c r="R25" t="n">
-        <v>6820599</v>
+        <v>6820411</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3160,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486719</v>
+        <v>121486611</v>
       </c>
       <c r="B26" t="n">
-        <v>78604</v>
+        <v>79717</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3172,25 +3159,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3200,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499078</v>
+        <v>499075</v>
       </c>
       <c r="R26" t="n">
-        <v>6820349</v>
+        <v>6820457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3262,10 +3249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486710</v>
+        <v>121486612</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>79717</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3274,25 +3261,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3302,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499134</v>
+        <v>499163</v>
       </c>
       <c r="R27" t="n">
-        <v>6820297</v>
+        <v>6820511</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,10 +3351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486748</v>
+        <v>121486637</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
+        <v>78344</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3380,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499224</v>
+        <v>499221</v>
       </c>
       <c r="R28" t="n">
-        <v>6820584</v>
+        <v>6820551</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486635</v>
+        <v>121486644</v>
       </c>
       <c r="B29" t="n">
-        <v>78341</v>
+        <v>98098</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3478,38 +3465,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499279</v>
+        <v>499088</v>
       </c>
       <c r="R29" t="n">
-        <v>6820470</v>
+        <v>6820326</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,6 +3545,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3568,10 +3564,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486720</v>
+        <v>121486731</v>
       </c>
       <c r="B30" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3608,10 +3604,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499064</v>
+        <v>499150</v>
       </c>
       <c r="R30" t="n">
-        <v>6820411</v>
+        <v>6820595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3670,10 +3666,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486714</v>
+        <v>121486719</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,10 +3706,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499120</v>
+        <v>499078</v>
       </c>
       <c r="R31" t="n">
-        <v>6820327</v>
+        <v>6820349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3772,10 +3768,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486652</v>
+        <v>121486717</v>
       </c>
       <c r="B32" t="n">
-        <v>78340</v>
+        <v>78607</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3788,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3812,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499247</v>
+        <v>499081</v>
       </c>
       <c r="R32" t="n">
-        <v>6820414</v>
+        <v>6820327</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3874,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486728</v>
+        <v>121486643</v>
       </c>
       <c r="B33" t="n">
-        <v>78604</v>
+        <v>80564</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3890,21 +3886,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3910,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499103</v>
+        <v>499159</v>
       </c>
       <c r="R33" t="n">
-        <v>6820567</v>
+        <v>6820599</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3976,10 +3972,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486654</v>
+        <v>121486626</v>
       </c>
       <c r="B34" t="n">
-        <v>78340</v>
+        <v>97052</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3988,25 +3984,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4016,10 +4012,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499174</v>
+        <v>499104</v>
       </c>
       <c r="R34" t="n">
-        <v>6820509</v>
+        <v>6820567</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4078,10 +4074,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486640</v>
+        <v>121486653</v>
       </c>
       <c r="B35" t="n">
-        <v>79685</v>
+        <v>78343</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4094,21 +4090,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4118,10 +4114,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499110</v>
+        <v>499063</v>
       </c>
       <c r="R35" t="n">
-        <v>6820446</v>
+        <v>6820418</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,10 +4176,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486711</v>
+        <v>121486766</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4196,21 +4192,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4220,10 +4216,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499126</v>
+        <v>499091</v>
       </c>
       <c r="R36" t="n">
-        <v>6820301</v>
+        <v>6820459</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4282,10 +4278,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486649</v>
+        <v>121486718</v>
       </c>
       <c r="B37" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4294,46 +4290,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499099</v>
+        <v>499079</v>
       </c>
       <c r="R37" t="n">
-        <v>6820449</v>
+        <v>6820344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4374,7 +4362,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4393,10 +4380,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486731</v>
+        <v>121486730</v>
       </c>
       <c r="B38" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4433,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499150</v>
+        <v>499159</v>
       </c>
       <c r="R38" t="n">
-        <v>6820595</v>
+        <v>6820605</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4495,10 +4482,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486592</v>
+        <v>121486629</v>
       </c>
       <c r="B39" t="n">
-        <v>74710</v>
+        <v>8435</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4507,38 +4494,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499180</v>
+        <v>499088</v>
       </c>
       <c r="R39" t="n">
-        <v>6820509</v>
+        <v>6820469</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,6 +4575,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4597,10 +4594,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486628</v>
+        <v>121486591</v>
       </c>
       <c r="B40" t="n">
-        <v>8432</v>
+        <v>74713</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4609,47 +4606,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499248</v>
+        <v>499060</v>
       </c>
       <c r="R40" t="n">
-        <v>6820414</v>
+        <v>6820434</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4684,18 +4672,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4714,10 +4696,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486743</v>
+        <v>121486740</v>
       </c>
       <c r="B41" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4754,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499204</v>
+        <v>499119</v>
       </c>
       <c r="R41" t="n">
-        <v>6820546</v>
+        <v>6820450</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4816,10 +4798,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486766</v>
+        <v>121486641</v>
       </c>
       <c r="B42" t="n">
-        <v>78340</v>
+        <v>79688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4832,21 +4814,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4856,10 +4838,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499091</v>
+        <v>499241</v>
       </c>
       <c r="R42" t="n">
-        <v>6820459</v>
+        <v>6820619</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4918,10 +4900,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486744</v>
+        <v>121486636</v>
       </c>
       <c r="B43" t="n">
-        <v>78604</v>
+        <v>78344</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4934,21 +4916,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4958,10 +4940,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499210</v>
+        <v>499244</v>
       </c>
       <c r="R43" t="n">
-        <v>6820548</v>
+        <v>6820418</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5020,10 +5002,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486587</v>
+        <v>121486623</v>
       </c>
       <c r="B44" t="n">
-        <v>79222</v>
+        <v>79689</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5036,21 +5018,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5060,10 +5042,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499137</v>
+        <v>499112</v>
       </c>
       <c r="R44" t="n">
-        <v>6820469</v>
+        <v>6820448</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5122,10 +5104,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486715</v>
+        <v>121486649</v>
       </c>
       <c r="B45" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5134,38 +5116,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499085</v>
+        <v>499099</v>
       </c>
       <c r="R45" t="n">
-        <v>6820324</v>
+        <v>6820449</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5206,6 +5196,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5224,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486721</v>
+        <v>121486651</v>
       </c>
       <c r="B46" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5240,21 +5231,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5264,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499066</v>
+        <v>499244</v>
       </c>
       <c r="R46" t="n">
-        <v>6820416</v>
+        <v>6820418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5326,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486703</v>
+        <v>121486715</v>
       </c>
       <c r="B47" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5366,10 +5357,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499321</v>
+        <v>499085</v>
       </c>
       <c r="R47" t="n">
-        <v>6820523</v>
+        <v>6820324</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5428,10 +5419,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486717</v>
+        <v>121486640</v>
       </c>
       <c r="B48" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5444,21 +5435,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5459,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499081</v>
+        <v>499110</v>
       </c>
       <c r="R48" t="n">
-        <v>6820327</v>
+        <v>6820446</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5521,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486623</v>
+        <v>121486586</v>
       </c>
       <c r="B49" t="n">
-        <v>79686</v>
+        <v>79225</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5546,21 +5537,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5561,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499112</v>
+        <v>499101</v>
       </c>
       <c r="R49" t="n">
-        <v>6820448</v>
+        <v>6820489</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5632,10 +5623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486722</v>
+        <v>121486652</v>
       </c>
       <c r="B50" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,21 +5639,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5672,10 +5663,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499063</v>
+        <v>499247</v>
       </c>
       <c r="R50" t="n">
-        <v>6820429</v>
+        <v>6820414</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5734,10 +5725,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486729</v>
+        <v>121486635</v>
       </c>
       <c r="B51" t="n">
-        <v>78604</v>
+        <v>78344</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,21 +5741,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5774,10 +5765,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499121</v>
+        <v>499279</v>
       </c>
       <c r="R51" t="n">
-        <v>6820578</v>
+        <v>6820470</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,10 +5827,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486730</v>
+        <v>121486648</v>
       </c>
       <c r="B52" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5848,38 +5839,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499159</v>
+        <v>499087</v>
       </c>
       <c r="R52" t="n">
-        <v>6820605</v>
+        <v>6820462</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5920,6 +5919,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>121475595</v>
       </c>
       <c r="B53" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>121475875</v>
       </c>
       <c r="B54" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486742</v>
+        <v>121486640</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499140</v>
+        <v>499110</v>
       </c>
       <c r="R2" t="n">
-        <v>6820485</v>
+        <v>6820446</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486739</v>
+        <v>121486744</v>
       </c>
       <c r="B3" t="n">
         <v>78607</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499079</v>
+        <v>499210</v>
       </c>
       <c r="R3" t="n">
-        <v>6820445</v>
+        <v>6820548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486587</v>
+        <v>121486637</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499137</v>
+        <v>499221</v>
       </c>
       <c r="R4" t="n">
-        <v>6820469</v>
+        <v>6820551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486703</v>
+        <v>121486586</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499321</v>
+        <v>499101</v>
       </c>
       <c r="R5" t="n">
-        <v>6820523</v>
+        <v>6820489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486738</v>
+        <v>121486629</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>8435</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499060</v>
+        <v>499088</v>
       </c>
       <c r="R6" t="n">
-        <v>6820435</v>
+        <v>6820469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1176,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486714</v>
+        <v>121486644</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1207,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499120</v>
+        <v>499088</v>
       </c>
       <c r="R7" t="n">
-        <v>6820327</v>
+        <v>6820326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1287,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486712</v>
+        <v>121486738</v>
       </c>
       <c r="B8" t="n">
         <v>78607</v>
@@ -1327,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499123</v>
+        <v>499060</v>
       </c>
       <c r="R8" t="n">
-        <v>6820315</v>
+        <v>6820435</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486729</v>
+        <v>121486636</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499121</v>
+        <v>499244</v>
       </c>
       <c r="R9" t="n">
-        <v>6820578</v>
+        <v>6820418</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486721</v>
+        <v>121486649</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1522,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499066</v>
+        <v>499099</v>
       </c>
       <c r="R10" t="n">
-        <v>6820416</v>
+        <v>6820449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,6 +1602,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1593,7 +1621,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486743</v>
+        <v>121486748</v>
       </c>
       <c r="B11" t="n">
         <v>78607</v>
@@ -1633,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499204</v>
+        <v>499224</v>
       </c>
       <c r="R11" t="n">
-        <v>6820546</v>
+        <v>6820584</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486592</v>
+        <v>121486743</v>
       </c>
       <c r="B12" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1739,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499180</v>
+        <v>499204</v>
       </c>
       <c r="R12" t="n">
-        <v>6820509</v>
+        <v>6820546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1825,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486711</v>
+        <v>121486721</v>
       </c>
       <c r="B13" t="n">
         <v>78607</v>
@@ -1837,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499126</v>
+        <v>499066</v>
       </c>
       <c r="R13" t="n">
-        <v>6820301</v>
+        <v>6820416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486628</v>
+        <v>121486703</v>
       </c>
       <c r="B14" t="n">
-        <v>8435</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,47 +1939,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499248</v>
+        <v>499321</v>
       </c>
       <c r="R14" t="n">
-        <v>6820414</v>
+        <v>6820523</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,18 +2005,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2016,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486658</v>
+        <v>121486712</v>
       </c>
       <c r="B15" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2045,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499221</v>
+        <v>499123</v>
       </c>
       <c r="R15" t="n">
-        <v>6820551</v>
+        <v>6820315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486713</v>
+        <v>121486658</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499123</v>
+        <v>499221</v>
       </c>
       <c r="R16" t="n">
-        <v>6820323</v>
+        <v>6820551</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486710</v>
+        <v>121486742</v>
       </c>
       <c r="B17" t="n">
         <v>78607</v>
@@ -2260,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499134</v>
+        <v>499140</v>
       </c>
       <c r="R17" t="n">
-        <v>6820297</v>
+        <v>6820485</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,7 +2335,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486745</v>
+        <v>121486729</v>
       </c>
       <c r="B18" t="n">
         <v>78607</v>
@@ -2362,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499219</v>
+        <v>499121</v>
       </c>
       <c r="R18" t="n">
-        <v>6820563</v>
+        <v>6820578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,7 +2437,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486744</v>
+        <v>121486715</v>
       </c>
       <c r="B19" t="n">
         <v>78607</v>
@@ -2464,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499210</v>
+        <v>499085</v>
       </c>
       <c r="R19" t="n">
-        <v>6820548</v>
+        <v>6820324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486654</v>
+        <v>121486745</v>
       </c>
       <c r="B20" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499174</v>
+        <v>499219</v>
       </c>
       <c r="R20" t="n">
-        <v>6820509</v>
+        <v>6820563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486728</v>
+        <v>121486643</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>80564</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499103</v>
+        <v>499159</v>
       </c>
       <c r="R21" t="n">
-        <v>6820567</v>
+        <v>6820599</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486646</v>
+        <v>121486713</v>
       </c>
       <c r="B22" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,46 +2755,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499124</v>
+        <v>499123</v>
       </c>
       <c r="R22" t="n">
-        <v>6820580</v>
+        <v>6820323</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,7 +2827,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2841,7 +2845,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486748</v>
+        <v>121486739</v>
       </c>
       <c r="B23" t="n">
         <v>78607</v>
@@ -2881,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499224</v>
+        <v>499079</v>
       </c>
       <c r="R23" t="n">
-        <v>6820584</v>
+        <v>6820445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,7 +2947,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486722</v>
+        <v>121486711</v>
       </c>
       <c r="B24" t="n">
         <v>78607</v>
@@ -2983,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499063</v>
+        <v>499126</v>
       </c>
       <c r="R24" t="n">
-        <v>6820429</v>
+        <v>6820301</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,7 +3049,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486720</v>
+        <v>121486714</v>
       </c>
       <c r="B25" t="n">
         <v>78607</v>
@@ -3085,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499064</v>
+        <v>499120</v>
       </c>
       <c r="R25" t="n">
-        <v>6820411</v>
+        <v>6820327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,10 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486611</v>
+        <v>121486722</v>
       </c>
       <c r="B26" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,25 +3163,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499075</v>
+        <v>499063</v>
       </c>
       <c r="R26" t="n">
-        <v>6820457</v>
+        <v>6820429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486612</v>
+        <v>121486719</v>
       </c>
       <c r="B27" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,25 +3265,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499163</v>
+        <v>499078</v>
       </c>
       <c r="R27" t="n">
-        <v>6820511</v>
+        <v>6820349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,10 +3355,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486637</v>
+        <v>121486720</v>
       </c>
       <c r="B28" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3367,21 +3371,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3391,10 +3395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499221</v>
+        <v>499064</v>
       </c>
       <c r="R28" t="n">
-        <v>6820551</v>
+        <v>6820411</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486644</v>
+        <v>121486718</v>
       </c>
       <c r="B29" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,46 +3469,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499088</v>
+        <v>499079</v>
       </c>
       <c r="R29" t="n">
-        <v>6820326</v>
+        <v>6820344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,7 +3541,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3564,10 +3559,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486731</v>
+        <v>121486654</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3580,21 +3575,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3604,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499150</v>
+        <v>499174</v>
       </c>
       <c r="R30" t="n">
-        <v>6820595</v>
+        <v>6820509</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3666,10 +3661,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486719</v>
+        <v>121486651</v>
       </c>
       <c r="B31" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3682,21 +3677,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3706,10 +3701,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499078</v>
+        <v>499244</v>
       </c>
       <c r="R31" t="n">
-        <v>6820349</v>
+        <v>6820418</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3768,10 +3763,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486717</v>
+        <v>121486623</v>
       </c>
       <c r="B32" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3784,21 +3779,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499081</v>
+        <v>499112</v>
       </c>
       <c r="R32" t="n">
-        <v>6820327</v>
+        <v>6820448</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486643</v>
+        <v>121486628</v>
       </c>
       <c r="B33" t="n">
-        <v>80564</v>
+        <v>8435</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3882,38 +3877,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499159</v>
+        <v>499248</v>
       </c>
       <c r="R33" t="n">
-        <v>6820599</v>
+        <v>6820414</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,12 +3952,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3972,10 +3982,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486626</v>
+        <v>121486766</v>
       </c>
       <c r="B34" t="n">
-        <v>97052</v>
+        <v>78343</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3984,25 +3994,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4012,10 +4022,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499104</v>
+        <v>499091</v>
       </c>
       <c r="R34" t="n">
-        <v>6820567</v>
+        <v>6820459</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4074,10 +4084,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486653</v>
+        <v>121486587</v>
       </c>
       <c r="B35" t="n">
-        <v>78343</v>
+        <v>79225</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4090,21 +4100,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4114,10 +4124,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499063</v>
+        <v>499137</v>
       </c>
       <c r="R35" t="n">
-        <v>6820418</v>
+        <v>6820469</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4176,10 +4186,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486766</v>
+        <v>121486710</v>
       </c>
       <c r="B36" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4192,21 +4202,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499091</v>
+        <v>499134</v>
       </c>
       <c r="R36" t="n">
-        <v>6820459</v>
+        <v>6820297</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4278,10 +4288,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486718</v>
+        <v>121486611</v>
       </c>
       <c r="B37" t="n">
-        <v>78607</v>
+        <v>79717</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4290,25 +4300,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4318,10 +4328,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499079</v>
+        <v>499075</v>
       </c>
       <c r="R37" t="n">
-        <v>6820344</v>
+        <v>6820457</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,7 +4390,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486730</v>
+        <v>121486728</v>
       </c>
       <c r="B38" t="n">
         <v>78607</v>
@@ -4420,10 +4430,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499159</v>
+        <v>499103</v>
       </c>
       <c r="R38" t="n">
-        <v>6820605</v>
+        <v>6820567</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4482,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486629</v>
+        <v>121486731</v>
       </c>
       <c r="B39" t="n">
-        <v>8435</v>
+        <v>78607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4494,47 +4504,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499088</v>
+        <v>499150</v>
       </c>
       <c r="R39" t="n">
-        <v>6820469</v>
+        <v>6820595</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4575,7 +4576,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4594,10 +4594,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486591</v>
+        <v>121486730</v>
       </c>
       <c r="B40" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4610,21 +4610,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499060</v>
+        <v>499159</v>
       </c>
       <c r="R40" t="n">
-        <v>6820434</v>
+        <v>6820605</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486740</v>
+        <v>121486641</v>
       </c>
       <c r="B41" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4712,21 +4712,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499119</v>
+        <v>499241</v>
       </c>
       <c r="R41" t="n">
-        <v>6820450</v>
+        <v>6820619</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486641</v>
+        <v>121486648</v>
       </c>
       <c r="B42" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,38 +4810,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499241</v>
+        <v>499087</v>
       </c>
       <c r="R42" t="n">
-        <v>6820619</v>
+        <v>6820462</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,6 +4890,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4900,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486636</v>
+        <v>121486591</v>
       </c>
       <c r="B43" t="n">
-        <v>78344</v>
+        <v>74713</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4916,21 +4925,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4940,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499244</v>
+        <v>499060</v>
       </c>
       <c r="R43" t="n">
-        <v>6820418</v>
+        <v>6820434</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5002,10 +5011,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486623</v>
+        <v>121486612</v>
       </c>
       <c r="B44" t="n">
-        <v>79689</v>
+        <v>79717</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5014,25 +5023,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5042,10 +5051,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499112</v>
+        <v>499163</v>
       </c>
       <c r="R44" t="n">
-        <v>6820448</v>
+        <v>6820511</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5104,10 +5113,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486649</v>
+        <v>121486740</v>
       </c>
       <c r="B45" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5116,46 +5125,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499099</v>
+        <v>499119</v>
       </c>
       <c r="R45" t="n">
-        <v>6820449</v>
+        <v>6820450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5196,7 +5197,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5215,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486651</v>
+        <v>121486635</v>
       </c>
       <c r="B46" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5231,21 +5231,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499244</v>
+        <v>499279</v>
       </c>
       <c r="R46" t="n">
-        <v>6820418</v>
+        <v>6820470</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486715</v>
+        <v>121486626</v>
       </c>
       <c r="B47" t="n">
-        <v>78607</v>
+        <v>97052</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5329,25 +5329,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499085</v>
+        <v>499104</v>
       </c>
       <c r="R47" t="n">
-        <v>6820324</v>
+        <v>6820567</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486640</v>
+        <v>121486717</v>
       </c>
       <c r="B48" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5435,21 +5435,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499110</v>
+        <v>499081</v>
       </c>
       <c r="R48" t="n">
-        <v>6820446</v>
+        <v>6820327</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486586</v>
+        <v>121486652</v>
       </c>
       <c r="B49" t="n">
-        <v>79225</v>
+        <v>78343</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5537,21 +5537,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499101</v>
+        <v>499247</v>
       </c>
       <c r="R49" t="n">
-        <v>6820489</v>
+        <v>6820414</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5623,7 +5623,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486652</v>
+        <v>121486653</v>
       </c>
       <c r="B50" t="n">
         <v>78343</v>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499247</v>
+        <v>499063</v>
       </c>
       <c r="R50" t="n">
-        <v>6820414</v>
+        <v>6820418</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5725,10 +5725,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486635</v>
+        <v>121486592</v>
       </c>
       <c r="B51" t="n">
-        <v>78344</v>
+        <v>74713</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5741,21 +5741,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499279</v>
+        <v>499180</v>
       </c>
       <c r="R51" t="n">
-        <v>6820470</v>
+        <v>6820509</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5827,7 +5827,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486648</v>
+        <v>121486646</v>
       </c>
       <c r="B52" t="n">
         <v>98098</v>
@@ -5875,10 +5875,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499087</v>
+        <v>499124</v>
       </c>
       <c r="R52" t="n">
-        <v>6820462</v>
+        <v>6820580</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121475595</v>
+        <v>121475875</v>
       </c>
       <c r="B53" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5954,34 +5954,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
+          <t>Långtallarna, Långtallarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499216</v>
+        <v>499095</v>
       </c>
       <c r="R53" t="n">
-        <v>6820553</v>
+        <v>6820473</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6050,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121475875</v>
+        <v>121475595</v>
       </c>
       <c r="B54" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6066,34 +6066,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långtallarna, Långtallarna, Dlr</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499095</v>
+        <v>499216</v>
       </c>
       <c r="R54" t="n">
-        <v>6820473</v>
+        <v>6820553</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486586</v>
+        <v>121486629</v>
       </c>
       <c r="B5" t="n">
-        <v>79225</v>
+        <v>8435</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499101</v>
+        <v>499088</v>
       </c>
       <c r="R5" t="n">
-        <v>6820489</v>
+        <v>6820469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486629</v>
+        <v>121486586</v>
       </c>
       <c r="B6" t="n">
-        <v>8435</v>
+        <v>79225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,47 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499088</v>
+        <v>499101</v>
       </c>
       <c r="R6" t="n">
-        <v>6820469</v>
+        <v>6820489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486745</v>
+        <v>121486643</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>80564</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499219</v>
+        <v>499159</v>
       </c>
       <c r="R20" t="n">
-        <v>6820563</v>
+        <v>6820599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486643</v>
+        <v>121486745</v>
       </c>
       <c r="B21" t="n">
-        <v>80564</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499159</v>
+        <v>499219</v>
       </c>
       <c r="R21" t="n">
-        <v>6820599</v>
+        <v>6820563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486740</v>
+        <v>121486635</v>
       </c>
       <c r="B45" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5129,21 +5129,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499119</v>
+        <v>499279</v>
       </c>
       <c r="R45" t="n">
-        <v>6820450</v>
+        <v>6820470</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486635</v>
+        <v>121486626</v>
       </c>
       <c r="B46" t="n">
-        <v>78344</v>
+        <v>97052</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5227,25 +5227,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499279</v>
+        <v>499104</v>
       </c>
       <c r="R46" t="n">
-        <v>6820470</v>
+        <v>6820567</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486626</v>
+        <v>121486740</v>
       </c>
       <c r="B47" t="n">
-        <v>97052</v>
+        <v>78607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5329,25 +5329,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499104</v>
+        <v>499119</v>
       </c>
       <c r="R47" t="n">
-        <v>6820567</v>
+        <v>6820450</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486717</v>
+        <v>121486652</v>
       </c>
       <c r="B48" t="n">
-        <v>78607</v>
+        <v>78343</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5435,21 +5435,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499081</v>
+        <v>499247</v>
       </c>
       <c r="R48" t="n">
-        <v>6820327</v>
+        <v>6820414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486652</v>
+        <v>121486653</v>
       </c>
       <c r="B49" t="n">
         <v>78343</v>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499247</v>
+        <v>499063</v>
       </c>
       <c r="R49" t="n">
-        <v>6820414</v>
+        <v>6820418</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486653</v>
+        <v>121486592</v>
       </c>
       <c r="B50" t="n">
-        <v>78343</v>
+        <v>74713</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5639,21 +5639,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499063</v>
+        <v>499180</v>
       </c>
       <c r="R50" t="n">
-        <v>6820418</v>
+        <v>6820509</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5725,10 +5725,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486592</v>
+        <v>121486646</v>
       </c>
       <c r="B51" t="n">
-        <v>74713</v>
+        <v>98098</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5737,38 +5737,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499180</v>
+        <v>499124</v>
       </c>
       <c r="R51" t="n">
-        <v>6820509</v>
+        <v>6820580</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5809,6 +5817,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5827,10 +5836,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486646</v>
+        <v>121486717</v>
       </c>
       <c r="B52" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5839,46 +5848,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499124</v>
+        <v>499081</v>
       </c>
       <c r="R52" t="n">
-        <v>6820580</v>
+        <v>6820327</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5919,7 +5920,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486629</v>
+        <v>121486586</v>
       </c>
       <c r="B5" t="n">
-        <v>8435</v>
+        <v>79225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499088</v>
+        <v>499101</v>
       </c>
       <c r="R5" t="n">
-        <v>6820469</v>
+        <v>6820489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486586</v>
+        <v>121486629</v>
       </c>
       <c r="B6" t="n">
-        <v>79225</v>
+        <v>8435</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1095,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499101</v>
+        <v>499088</v>
       </c>
       <c r="R6" t="n">
-        <v>6820489</v>
+        <v>6820469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1176,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486643</v>
+        <v>121486745</v>
       </c>
       <c r="B20" t="n">
-        <v>80564</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499159</v>
+        <v>499219</v>
       </c>
       <c r="R20" t="n">
-        <v>6820599</v>
+        <v>6820563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486745</v>
+        <v>121486643</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>80564</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499219</v>
+        <v>499159</v>
       </c>
       <c r="R21" t="n">
-        <v>6820563</v>
+        <v>6820599</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3865,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486628</v>
+        <v>121486710</v>
       </c>
       <c r="B33" t="n">
-        <v>8435</v>
+        <v>78607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,47 +3877,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499248</v>
+        <v>499134</v>
       </c>
       <c r="R33" t="n">
-        <v>6820414</v>
+        <v>6820297</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,18 +3943,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4186,10 +4171,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486710</v>
+        <v>121486628</v>
       </c>
       <c r="B36" t="n">
-        <v>78607</v>
+        <v>8435</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4198,38 +4183,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499134</v>
+        <v>499248</v>
       </c>
       <c r="R36" t="n">
-        <v>6820297</v>
+        <v>6820414</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,12 +4258,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486635</v>
+        <v>121486740</v>
       </c>
       <c r="B45" t="n">
-        <v>78344</v>
+        <v>78607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5129,21 +5129,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499279</v>
+        <v>499119</v>
       </c>
       <c r="R45" t="n">
-        <v>6820470</v>
+        <v>6820450</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486626</v>
+        <v>121486635</v>
       </c>
       <c r="B46" t="n">
-        <v>97052</v>
+        <v>78344</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5227,25 +5227,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499104</v>
+        <v>499279</v>
       </c>
       <c r="R46" t="n">
-        <v>6820567</v>
+        <v>6820470</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486740</v>
+        <v>121486626</v>
       </c>
       <c r="B47" t="n">
-        <v>78607</v>
+        <v>97052</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5329,25 +5329,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499119</v>
+        <v>499104</v>
       </c>
       <c r="R47" t="n">
-        <v>6820450</v>
+        <v>6820567</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486652</v>
+        <v>121486717</v>
       </c>
       <c r="B48" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5435,21 +5435,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499247</v>
+        <v>499081</v>
       </c>
       <c r="R48" t="n">
-        <v>6820414</v>
+        <v>6820327</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486653</v>
+        <v>121486652</v>
       </c>
       <c r="B49" t="n">
         <v>78343</v>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499063</v>
+        <v>499247</v>
       </c>
       <c r="R49" t="n">
-        <v>6820418</v>
+        <v>6820414</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486592</v>
+        <v>121486653</v>
       </c>
       <c r="B50" t="n">
-        <v>74713</v>
+        <v>78343</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5639,21 +5639,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499180</v>
+        <v>499063</v>
       </c>
       <c r="R50" t="n">
-        <v>6820509</v>
+        <v>6820418</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5725,10 +5725,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486646</v>
+        <v>121486592</v>
       </c>
       <c r="B51" t="n">
-        <v>98098</v>
+        <v>74713</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5737,46 +5737,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499124</v>
+        <v>499180</v>
       </c>
       <c r="R51" t="n">
-        <v>6820580</v>
+        <v>6820509</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5817,7 +5809,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5836,10 +5827,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486717</v>
+        <v>121486646</v>
       </c>
       <c r="B52" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5848,38 +5839,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499081</v>
+        <v>499124</v>
       </c>
       <c r="R52" t="n">
-        <v>6820327</v>
+        <v>6820580</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5920,6 +5919,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486640</v>
+        <v>121486722</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499110</v>
+        <v>499063</v>
       </c>
       <c r="R2" t="n">
-        <v>6820446</v>
+        <v>6820429</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486744</v>
+        <v>121486711</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499210</v>
+        <v>499126</v>
       </c>
       <c r="R3" t="n">
-        <v>6820548</v>
+        <v>6820301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486637</v>
+        <v>121486654</v>
       </c>
       <c r="B4" t="n">
         <v>78344</v>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499221</v>
+        <v>499174</v>
       </c>
       <c r="R4" t="n">
-        <v>6820551</v>
+        <v>6820509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486586</v>
+        <v>121486635</v>
       </c>
       <c r="B5" t="n">
-        <v>79225</v>
+        <v>78345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499101</v>
+        <v>499279</v>
       </c>
       <c r="R5" t="n">
-        <v>6820489</v>
+        <v>6820470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486629</v>
+        <v>121486712</v>
       </c>
       <c r="B6" t="n">
-        <v>8435</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,47 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499088</v>
+        <v>499123</v>
       </c>
       <c r="R6" t="n">
-        <v>6820469</v>
+        <v>6820315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486644</v>
+        <v>121486738</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,46 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499088</v>
+        <v>499060</v>
       </c>
       <c r="R7" t="n">
-        <v>6820326</v>
+        <v>6820435</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1306,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486738</v>
+        <v>121486717</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499060</v>
+        <v>499081</v>
       </c>
       <c r="R8" t="n">
-        <v>6820435</v>
+        <v>6820327</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486636</v>
+        <v>121486626</v>
       </c>
       <c r="B9" t="n">
-        <v>78344</v>
+        <v>97058</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499244</v>
+        <v>499104</v>
       </c>
       <c r="R9" t="n">
-        <v>6820418</v>
+        <v>6820567</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486649</v>
+        <v>121486729</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,46 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499099</v>
+        <v>499121</v>
       </c>
       <c r="R10" t="n">
-        <v>6820449</v>
+        <v>6820578</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1575,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1621,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486748</v>
+        <v>121486653</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1661,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499224</v>
+        <v>499063</v>
       </c>
       <c r="R11" t="n">
-        <v>6820584</v>
+        <v>6820418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486743</v>
+        <v>121486641</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499204</v>
+        <v>499241</v>
       </c>
       <c r="R12" t="n">
-        <v>6820546</v>
+        <v>6820619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486721</v>
+        <v>121486629</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>8435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,38 +1809,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499066</v>
+        <v>499088</v>
       </c>
       <c r="R13" t="n">
-        <v>6820416</v>
+        <v>6820469</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,6 +1890,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1927,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486703</v>
+        <v>121486740</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499321</v>
+        <v>499119</v>
       </c>
       <c r="R14" t="n">
-        <v>6820523</v>
+        <v>6820450</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486712</v>
+        <v>121486703</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499123</v>
+        <v>499321</v>
       </c>
       <c r="R15" t="n">
-        <v>6820315</v>
+        <v>6820523</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486658</v>
+        <v>121486592</v>
       </c>
       <c r="B16" t="n">
-        <v>78343</v>
+        <v>74714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499221</v>
+        <v>499180</v>
       </c>
       <c r="R16" t="n">
-        <v>6820551</v>
+        <v>6820509</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486742</v>
+        <v>121486587</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499140</v>
+        <v>499137</v>
       </c>
       <c r="R17" t="n">
-        <v>6820485</v>
+        <v>6820469</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486729</v>
+        <v>121486743</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499121</v>
+        <v>499204</v>
       </c>
       <c r="R18" t="n">
-        <v>6820578</v>
+        <v>6820546</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486715</v>
+        <v>121486731</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2477,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499085</v>
+        <v>499150</v>
       </c>
       <c r="R19" t="n">
-        <v>6820324</v>
+        <v>6820595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486745</v>
+        <v>121486721</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499219</v>
+        <v>499066</v>
       </c>
       <c r="R20" t="n">
-        <v>6820563</v>
+        <v>6820416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486643</v>
+        <v>121486730</v>
       </c>
       <c r="B21" t="n">
-        <v>80564</v>
+        <v>78608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2684,7 +2666,7 @@
         <v>499159</v>
       </c>
       <c r="R21" t="n">
-        <v>6820599</v>
+        <v>6820605</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2743,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486713</v>
+        <v>121486612</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>79718</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2783,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499123</v>
+        <v>499163</v>
       </c>
       <c r="R22" t="n">
-        <v>6820323</v>
+        <v>6820511</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2845,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486739</v>
+        <v>121486649</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,38 +2839,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499079</v>
+        <v>499099</v>
       </c>
       <c r="R23" t="n">
-        <v>6820445</v>
+        <v>6820449</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,6 +2919,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2947,10 +2938,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486711</v>
+        <v>121486745</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2987,10 +2978,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499126</v>
+        <v>499219</v>
       </c>
       <c r="R24" t="n">
-        <v>6820301</v>
+        <v>6820563</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3049,10 +3040,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486714</v>
+        <v>121486742</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3089,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499120</v>
+        <v>499140</v>
       </c>
       <c r="R25" t="n">
-        <v>6820327</v>
+        <v>6820485</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3151,10 +3142,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486722</v>
+        <v>121486720</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3191,10 +3182,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499063</v>
+        <v>499064</v>
       </c>
       <c r="R26" t="n">
-        <v>6820429</v>
+        <v>6820411</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,10 +3244,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486719</v>
+        <v>121486643</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>80565</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3269,21 +3260,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3284,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499078</v>
+        <v>499159</v>
       </c>
       <c r="R27" t="n">
-        <v>6820349</v>
+        <v>6820599</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3355,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486720</v>
+        <v>121486652</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3371,21 +3362,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3395,10 +3386,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499064</v>
+        <v>499247</v>
       </c>
       <c r="R28" t="n">
-        <v>6820411</v>
+        <v>6820414</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3457,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486718</v>
+        <v>121486658</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3473,21 +3464,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3497,10 +3488,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499079</v>
+        <v>499221</v>
       </c>
       <c r="R29" t="n">
-        <v>6820344</v>
+        <v>6820551</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3559,10 +3550,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486654</v>
+        <v>121486651</v>
       </c>
       <c r="B30" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3599,10 +3590,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499174</v>
+        <v>499244</v>
       </c>
       <c r="R30" t="n">
-        <v>6820509</v>
+        <v>6820418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486651</v>
+        <v>121486744</v>
       </c>
       <c r="B31" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3677,21 +3668,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3701,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499244</v>
+        <v>499210</v>
       </c>
       <c r="R31" t="n">
-        <v>6820418</v>
+        <v>6820548</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3763,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486623</v>
+        <v>121486644</v>
       </c>
       <c r="B32" t="n">
-        <v>79689</v>
+        <v>98104</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,38 +3766,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499112</v>
+        <v>499088</v>
       </c>
       <c r="R32" t="n">
-        <v>6820448</v>
+        <v>6820326</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,6 +3846,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>121486710</v>
       </c>
       <c r="B33" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>121486766</v>
       </c>
       <c r="B34" t="n">
-        <v>78343</v>
+        <v>78344</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,10 +4069,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486587</v>
+        <v>121486628</v>
       </c>
       <c r="B35" t="n">
-        <v>79225</v>
+        <v>8435</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,38 +4081,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499137</v>
+        <v>499248</v>
       </c>
       <c r="R35" t="n">
-        <v>6820469</v>
+        <v>6820414</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4147,12 +4156,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4171,10 +4186,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486628</v>
+        <v>121486637</v>
       </c>
       <c r="B36" t="n">
-        <v>8435</v>
+        <v>78345</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,47 +4198,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499248</v>
+        <v>499221</v>
       </c>
       <c r="R36" t="n">
-        <v>6820414</v>
+        <v>6820551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,18 +4264,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4288,10 +4288,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486611</v>
+        <v>121486739</v>
       </c>
       <c r="B37" t="n">
-        <v>79717</v>
+        <v>78608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4300,25 +4300,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499075</v>
+        <v>499079</v>
       </c>
       <c r="R37" t="n">
-        <v>6820457</v>
+        <v>6820445</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4393,7 +4393,7 @@
         <v>121486728</v>
       </c>
       <c r="B38" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486731</v>
+        <v>121486640</v>
       </c>
       <c r="B39" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4508,21 +4508,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499150</v>
+        <v>499110</v>
       </c>
       <c r="R39" t="n">
-        <v>6820595</v>
+        <v>6820446</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,10 +4594,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486730</v>
+        <v>121486748</v>
       </c>
       <c r="B40" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499159</v>
+        <v>499224</v>
       </c>
       <c r="R40" t="n">
-        <v>6820605</v>
+        <v>6820584</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486641</v>
+        <v>121486714</v>
       </c>
       <c r="B41" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4712,21 +4712,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499241</v>
+        <v>499120</v>
       </c>
       <c r="R41" t="n">
-        <v>6820619</v>
+        <v>6820327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486648</v>
+        <v>121486623</v>
       </c>
       <c r="B42" t="n">
-        <v>98098</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,46 +4810,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499087</v>
+        <v>499112</v>
       </c>
       <c r="R42" t="n">
-        <v>6820462</v>
+        <v>6820448</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4890,7 +4882,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4909,10 +4900,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486591</v>
+        <v>121486719</v>
       </c>
       <c r="B43" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4925,21 +4916,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4940,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499060</v>
+        <v>499078</v>
       </c>
       <c r="R43" t="n">
-        <v>6820434</v>
+        <v>6820349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5011,10 +5002,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486612</v>
+        <v>121486586</v>
       </c>
       <c r="B44" t="n">
-        <v>79717</v>
+        <v>79226</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5023,25 +5014,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5051,10 +5042,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499163</v>
+        <v>499101</v>
       </c>
       <c r="R44" t="n">
-        <v>6820511</v>
+        <v>6820489</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5113,10 +5104,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486740</v>
+        <v>121486591</v>
       </c>
       <c r="B45" t="n">
-        <v>78607</v>
+        <v>74714</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5129,21 +5120,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5153,10 +5144,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499119</v>
+        <v>499060</v>
       </c>
       <c r="R45" t="n">
-        <v>6820450</v>
+        <v>6820434</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,10 +5206,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486635</v>
+        <v>121486611</v>
       </c>
       <c r="B46" t="n">
-        <v>78344</v>
+        <v>79718</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5227,25 +5218,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +5246,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499279</v>
+        <v>499075</v>
       </c>
       <c r="R46" t="n">
-        <v>6820470</v>
+        <v>6820457</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,10 +5308,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486626</v>
+        <v>121486646</v>
       </c>
       <c r="B47" t="n">
-        <v>97052</v>
+        <v>98104</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5329,38 +5320,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499104</v>
+        <v>499124</v>
       </c>
       <c r="R47" t="n">
-        <v>6820567</v>
+        <v>6820580</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5401,6 +5400,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486717</v>
+        <v>121486636</v>
       </c>
       <c r="B48" t="n">
-        <v>78607</v>
+        <v>78345</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5435,21 +5435,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499081</v>
+        <v>499244</v>
       </c>
       <c r="R48" t="n">
-        <v>6820327</v>
+        <v>6820418</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486652</v>
+        <v>121486718</v>
       </c>
       <c r="B49" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5537,21 +5537,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499247</v>
+        <v>499079</v>
       </c>
       <c r="R49" t="n">
-        <v>6820414</v>
+        <v>6820344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5623,10 +5623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486653</v>
+        <v>121486648</v>
       </c>
       <c r="B50" t="n">
-        <v>78343</v>
+        <v>98104</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5635,38 +5635,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499063</v>
+        <v>499087</v>
       </c>
       <c r="R50" t="n">
-        <v>6820418</v>
+        <v>6820462</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5707,6 +5715,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5725,10 +5734,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486592</v>
+        <v>121486715</v>
       </c>
       <c r="B51" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5741,21 +5750,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5765,10 +5774,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499180</v>
+        <v>499085</v>
       </c>
       <c r="R51" t="n">
-        <v>6820509</v>
+        <v>6820324</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5827,10 +5836,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486646</v>
+        <v>121486713</v>
       </c>
       <c r="B52" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5839,46 +5848,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499124</v>
+        <v>499123</v>
       </c>
       <c r="R52" t="n">
-        <v>6820580</v>
+        <v>6820323</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5919,7 +5920,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121475875</v>
+        <v>121475595</v>
       </c>
       <c r="B53" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5954,34 +5954,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långtallarna, Långtallarna, Dlr</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499095</v>
+        <v>499216</v>
       </c>
       <c r="R53" t="n">
-        <v>6820473</v>
+        <v>6820553</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6050,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121475595</v>
+        <v>121475875</v>
       </c>
       <c r="B54" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6066,34 +6066,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
+          <t>Långtallarna, Långtallarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499216</v>
+        <v>499095</v>
       </c>
       <c r="R54" t="n">
-        <v>6820553</v>
+        <v>6820473</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486635</v>
+        <v>121486712</v>
       </c>
       <c r="B5" t="n">
-        <v>78345</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499279</v>
+        <v>499123</v>
       </c>
       <c r="R5" t="n">
-        <v>6820470</v>
+        <v>6820315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486712</v>
+        <v>121486635</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499123</v>
+        <v>499279</v>
       </c>
       <c r="R6" t="n">
-        <v>6820315</v>
+        <v>6820470</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -4594,10 +4594,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486748</v>
+        <v>121486623</v>
       </c>
       <c r="B40" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4610,21 +4610,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499224</v>
+        <v>499112</v>
       </c>
       <c r="R40" t="n">
-        <v>6820584</v>
+        <v>6820448</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4696,7 +4696,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486714</v>
+        <v>121486748</v>
       </c>
       <c r="B41" t="n">
         <v>78608</v>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499120</v>
+        <v>499224</v>
       </c>
       <c r="R41" t="n">
-        <v>6820327</v>
+        <v>6820584</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4798,10 +4798,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486623</v>
+        <v>121486714</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>78608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4814,21 +4814,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4838,10 +4838,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499112</v>
+        <v>499120</v>
       </c>
       <c r="R42" t="n">
-        <v>6820448</v>
+        <v>6820327</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486722</v>
+        <v>121486743</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499063</v>
+        <v>499204</v>
       </c>
       <c r="R2" t="n">
-        <v>6820429</v>
+        <v>6820546</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486711</v>
+        <v>121486719</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499126</v>
+        <v>499078</v>
       </c>
       <c r="R3" t="n">
-        <v>6820301</v>
+        <v>6820349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486654</v>
+        <v>121486720</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499174</v>
+        <v>499064</v>
       </c>
       <c r="R4" t="n">
-        <v>6820509</v>
+        <v>6820411</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486712</v>
+        <v>121486658</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499123</v>
+        <v>499221</v>
       </c>
       <c r="R5" t="n">
-        <v>6820315</v>
+        <v>6820551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486635</v>
+        <v>121486648</v>
       </c>
       <c r="B6" t="n">
-        <v>78345</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499279</v>
+        <v>499087</v>
       </c>
       <c r="R6" t="n">
-        <v>6820470</v>
+        <v>6820462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1175,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486738</v>
+        <v>121486635</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>78346</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499060</v>
+        <v>499279</v>
       </c>
       <c r="R7" t="n">
-        <v>6820435</v>
+        <v>6820470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486717</v>
+        <v>121486587</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>79227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499081</v>
+        <v>499137</v>
       </c>
       <c r="R8" t="n">
-        <v>6820327</v>
+        <v>6820469</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486626</v>
+        <v>121486623</v>
       </c>
       <c r="B9" t="n">
-        <v>97058</v>
+        <v>79691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499104</v>
+        <v>499112</v>
       </c>
       <c r="R9" t="n">
-        <v>6820567</v>
+        <v>6820448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486729</v>
+        <v>121486715</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499121</v>
+        <v>499085</v>
       </c>
       <c r="R10" t="n">
-        <v>6820578</v>
+        <v>6820324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486653</v>
+        <v>121486592</v>
       </c>
       <c r="B11" t="n">
-        <v>78344</v>
+        <v>74715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499063</v>
+        <v>499180</v>
       </c>
       <c r="R11" t="n">
-        <v>6820418</v>
+        <v>6820509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486641</v>
+        <v>121486637</v>
       </c>
       <c r="B12" t="n">
-        <v>79689</v>
+        <v>78346</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499241</v>
+        <v>499221</v>
       </c>
       <c r="R12" t="n">
-        <v>6820619</v>
+        <v>6820551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486629</v>
+        <v>121486721</v>
       </c>
       <c r="B13" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,47 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499088</v>
+        <v>499066</v>
       </c>
       <c r="R13" t="n">
-        <v>6820469</v>
+        <v>6820416</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,7 +1890,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1909,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486740</v>
+        <v>121486744</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499119</v>
+        <v>499210</v>
       </c>
       <c r="R14" t="n">
-        <v>6820450</v>
+        <v>6820548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486703</v>
+        <v>121486626</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>97059</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499321</v>
+        <v>499104</v>
       </c>
       <c r="R15" t="n">
-        <v>6820523</v>
+        <v>6820567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486592</v>
+        <v>121486728</v>
       </c>
       <c r="B16" t="n">
-        <v>74714</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499180</v>
+        <v>499103</v>
       </c>
       <c r="R16" t="n">
-        <v>6820509</v>
+        <v>6820567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486587</v>
+        <v>121486586</v>
       </c>
       <c r="B17" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499137</v>
+        <v>499101</v>
       </c>
       <c r="R17" t="n">
-        <v>6820469</v>
+        <v>6820489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486743</v>
+        <v>121486739</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2357,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499204</v>
+        <v>499079</v>
       </c>
       <c r="R18" t="n">
-        <v>6820546</v>
+        <v>6820445</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486731</v>
+        <v>121486644</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,38 +2430,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499150</v>
+        <v>499088</v>
       </c>
       <c r="R19" t="n">
-        <v>6820595</v>
+        <v>6820326</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,6 +2510,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486721</v>
+        <v>121486611</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>79719</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,25 +2541,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499066</v>
+        <v>499075</v>
       </c>
       <c r="R20" t="n">
-        <v>6820416</v>
+        <v>6820457</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486730</v>
+        <v>121486714</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2663,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499159</v>
+        <v>499120</v>
       </c>
       <c r="R21" t="n">
-        <v>6820605</v>
+        <v>6820327</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486612</v>
+        <v>121486717</v>
       </c>
       <c r="B22" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2745,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499163</v>
+        <v>499081</v>
       </c>
       <c r="R22" t="n">
-        <v>6820511</v>
+        <v>6820327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486649</v>
+        <v>121486748</v>
       </c>
       <c r="B23" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,46 +2847,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499099</v>
+        <v>499224</v>
       </c>
       <c r="R23" t="n">
-        <v>6820449</v>
+        <v>6820584</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2938,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486745</v>
+        <v>121486722</v>
       </c>
       <c r="B24" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2978,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499219</v>
+        <v>499063</v>
       </c>
       <c r="R24" t="n">
-        <v>6820563</v>
+        <v>6820429</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3040,10 +3039,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486742</v>
+        <v>121486729</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3080,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499140</v>
+        <v>499121</v>
       </c>
       <c r="R25" t="n">
-        <v>6820485</v>
+        <v>6820578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486720</v>
+        <v>121486740</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3182,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499064</v>
+        <v>499119</v>
       </c>
       <c r="R26" t="n">
-        <v>6820411</v>
+        <v>6820450</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486643</v>
+        <v>121486646</v>
       </c>
       <c r="B27" t="n">
-        <v>80565</v>
+        <v>98105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3256,38 +3255,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499159</v>
+        <v>499124</v>
       </c>
       <c r="R27" t="n">
-        <v>6820599</v>
+        <v>6820580</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3328,6 +3335,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3346,10 +3354,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486652</v>
+        <v>121486651</v>
       </c>
       <c r="B28" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3386,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499247</v>
+        <v>499244</v>
       </c>
       <c r="R28" t="n">
-        <v>6820414</v>
+        <v>6820418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,10 +3456,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486658</v>
+        <v>121486643</v>
       </c>
       <c r="B29" t="n">
-        <v>78344</v>
+        <v>80566</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3464,21 +3472,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3488,10 +3496,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499221</v>
+        <v>499159</v>
       </c>
       <c r="R29" t="n">
-        <v>6820551</v>
+        <v>6820599</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,10 +3558,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486651</v>
+        <v>121486766</v>
       </c>
       <c r="B30" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3590,10 +3598,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499244</v>
+        <v>499091</v>
       </c>
       <c r="R30" t="n">
-        <v>6820418</v>
+        <v>6820459</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,10 +3660,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486744</v>
+        <v>121486710</v>
       </c>
       <c r="B31" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3692,10 +3700,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499210</v>
+        <v>499134</v>
       </c>
       <c r="R31" t="n">
-        <v>6820548</v>
+        <v>6820297</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,10 +3762,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486644</v>
+        <v>121486629</v>
       </c>
       <c r="B32" t="n">
-        <v>98104</v>
+        <v>8435</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3766,35 +3774,36 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3805,7 +3814,7 @@
         <v>499088</v>
       </c>
       <c r="R32" t="n">
-        <v>6820326</v>
+        <v>6820469</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3865,10 +3874,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486710</v>
+        <v>121486711</v>
       </c>
       <c r="B33" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3905,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499134</v>
+        <v>499126</v>
       </c>
       <c r="R33" t="n">
-        <v>6820297</v>
+        <v>6820301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3976,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486766</v>
+        <v>121486703</v>
       </c>
       <c r="B34" t="n">
-        <v>78344</v>
+        <v>78609</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3983,21 +3992,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4007,10 +4016,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499091</v>
+        <v>499321</v>
       </c>
       <c r="R34" t="n">
-        <v>6820459</v>
+        <v>6820523</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4069,10 +4078,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486628</v>
+        <v>121486652</v>
       </c>
       <c r="B35" t="n">
-        <v>8435</v>
+        <v>78345</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,44 +4090,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499248</v>
+        <v>499247</v>
       </c>
       <c r="R35" t="n">
         <v>6820414</v>
@@ -4156,18 +4156,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4186,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486637</v>
+        <v>121486738</v>
       </c>
       <c r="B36" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4202,21 +4196,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4226,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499221</v>
+        <v>499060</v>
       </c>
       <c r="R36" t="n">
-        <v>6820551</v>
+        <v>6820435</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4288,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486739</v>
+        <v>121486640</v>
       </c>
       <c r="B37" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4304,21 +4298,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4328,10 +4322,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499079</v>
+        <v>499110</v>
       </c>
       <c r="R37" t="n">
-        <v>6820445</v>
+        <v>6820446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4390,10 +4384,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486728</v>
+        <v>121486745</v>
       </c>
       <c r="B38" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4430,10 +4424,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499103</v>
+        <v>499219</v>
       </c>
       <c r="R38" t="n">
-        <v>6820567</v>
+        <v>6820563</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,10 +4486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486640</v>
+        <v>121486730</v>
       </c>
       <c r="B39" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4508,21 +4502,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4532,10 +4526,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499110</v>
+        <v>499159</v>
       </c>
       <c r="R39" t="n">
-        <v>6820446</v>
+        <v>6820605</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,10 +4588,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486623</v>
+        <v>121486712</v>
       </c>
       <c r="B40" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4610,21 +4604,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4634,10 +4628,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499112</v>
+        <v>499123</v>
       </c>
       <c r="R40" t="n">
-        <v>6820448</v>
+        <v>6820315</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4696,10 +4690,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486748</v>
+        <v>121486731</v>
       </c>
       <c r="B41" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4736,10 +4730,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499224</v>
+        <v>499150</v>
       </c>
       <c r="R41" t="n">
-        <v>6820584</v>
+        <v>6820595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4798,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486714</v>
+        <v>121486636</v>
       </c>
       <c r="B42" t="n">
-        <v>78608</v>
+        <v>78346</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4814,21 +4808,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4838,10 +4832,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499120</v>
+        <v>499244</v>
       </c>
       <c r="R42" t="n">
-        <v>6820327</v>
+        <v>6820418</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4900,10 +4894,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486719</v>
+        <v>121486649</v>
       </c>
       <c r="B43" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4912,38 +4906,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499078</v>
+        <v>499099</v>
       </c>
       <c r="R43" t="n">
-        <v>6820349</v>
+        <v>6820449</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,6 +4986,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5002,10 +5005,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486586</v>
+        <v>121486713</v>
       </c>
       <c r="B44" t="n">
-        <v>79226</v>
+        <v>78609</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5018,21 +5021,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5042,10 +5045,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499101</v>
+        <v>499123</v>
       </c>
       <c r="R44" t="n">
-        <v>6820489</v>
+        <v>6820323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5104,10 +5107,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486591</v>
+        <v>121486742</v>
       </c>
       <c r="B45" t="n">
-        <v>74714</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5120,21 +5123,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5144,10 +5147,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499060</v>
+        <v>499140</v>
       </c>
       <c r="R45" t="n">
-        <v>6820434</v>
+        <v>6820485</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5206,10 +5209,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486611</v>
+        <v>121486718</v>
       </c>
       <c r="B46" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5218,25 +5221,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5246,10 +5249,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499075</v>
+        <v>499079</v>
       </c>
       <c r="R46" t="n">
-        <v>6820457</v>
+        <v>6820344</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5308,10 +5311,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486646</v>
+        <v>121486612</v>
       </c>
       <c r="B47" t="n">
-        <v>98104</v>
+        <v>79719</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5320,46 +5323,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499124</v>
+        <v>499163</v>
       </c>
       <c r="R47" t="n">
-        <v>6820580</v>
+        <v>6820511</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5400,7 +5395,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5419,10 +5413,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486636</v>
+        <v>121486628</v>
       </c>
       <c r="B48" t="n">
-        <v>78345</v>
+        <v>8435</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5431,38 +5425,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499244</v>
+        <v>499248</v>
       </c>
       <c r="R48" t="n">
-        <v>6820418</v>
+        <v>6820414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5497,12 +5500,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5521,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486718</v>
+        <v>121486591</v>
       </c>
       <c r="B49" t="n">
-        <v>78608</v>
+        <v>74715</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5537,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5561,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499079</v>
+        <v>499060</v>
       </c>
       <c r="R49" t="n">
-        <v>6820344</v>
+        <v>6820434</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5623,10 +5632,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486648</v>
+        <v>121486641</v>
       </c>
       <c r="B50" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5635,46 +5644,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499087</v>
+        <v>499241</v>
       </c>
       <c r="R50" t="n">
-        <v>6820462</v>
+        <v>6820619</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5715,7 +5716,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486715</v>
+        <v>121486654</v>
       </c>
       <c r="B51" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499085</v>
+        <v>499174</v>
       </c>
       <c r="R51" t="n">
-        <v>6820324</v>
+        <v>6820509</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486713</v>
+        <v>121486653</v>
       </c>
       <c r="B52" t="n">
-        <v>78608</v>
+        <v>78345</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499123</v>
+        <v>499063</v>
       </c>
       <c r="R52" t="n">
-        <v>6820323</v>
+        <v>6820418</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
         <v>121475595</v>
       </c>
       <c r="B53" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>121475875</v>
       </c>
       <c r="B54" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486743</v>
+        <v>121486714</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499204</v>
+        <v>499120</v>
       </c>
       <c r="R2" t="n">
-        <v>6820546</v>
+        <v>6820327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486719</v>
+        <v>121486612</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499078</v>
+        <v>499163</v>
       </c>
       <c r="R3" t="n">
-        <v>6820349</v>
+        <v>6820511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486720</v>
+        <v>121486592</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499064</v>
+        <v>499180</v>
       </c>
       <c r="R4" t="n">
-        <v>6820411</v>
+        <v>6820509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486658</v>
+        <v>121486652</v>
       </c>
       <c r="B5" t="n">
         <v>78345</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499221</v>
+        <v>499247</v>
       </c>
       <c r="R5" t="n">
-        <v>6820551</v>
+        <v>6820414</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486648</v>
+        <v>121486646</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499087</v>
+        <v>499124</v>
       </c>
       <c r="R6" t="n">
-        <v>6820462</v>
+        <v>6820580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486635</v>
+        <v>121486587</v>
       </c>
       <c r="B7" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499279</v>
+        <v>499137</v>
       </c>
       <c r="R7" t="n">
-        <v>6820470</v>
+        <v>6820469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486587</v>
+        <v>121486730</v>
       </c>
       <c r="B8" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499137</v>
+        <v>499159</v>
       </c>
       <c r="R8" t="n">
-        <v>6820469</v>
+        <v>6820605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486623</v>
+        <v>121486745</v>
       </c>
       <c r="B9" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499112</v>
+        <v>499219</v>
       </c>
       <c r="R9" t="n">
-        <v>6820448</v>
+        <v>6820563</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486715</v>
+        <v>121486658</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499085</v>
+        <v>499221</v>
       </c>
       <c r="R10" t="n">
-        <v>6820324</v>
+        <v>6820551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486592</v>
+        <v>121486703</v>
       </c>
       <c r="B11" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499180</v>
+        <v>499321</v>
       </c>
       <c r="R11" t="n">
-        <v>6820509</v>
+        <v>6820523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486637</v>
+        <v>121486629</v>
       </c>
       <c r="B12" t="n">
-        <v>78346</v>
+        <v>8435</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,38 +1716,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499221</v>
+        <v>499088</v>
       </c>
       <c r="R12" t="n">
-        <v>6820551</v>
+        <v>6820469</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1797,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1806,7 +1816,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486721</v>
+        <v>121486715</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1846,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499066</v>
+        <v>499085</v>
       </c>
       <c r="R13" t="n">
-        <v>6820416</v>
+        <v>6820324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486744</v>
+        <v>121486651</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499210</v>
+        <v>499244</v>
       </c>
       <c r="R14" t="n">
-        <v>6820548</v>
+        <v>6820418</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486626</v>
+        <v>121486717</v>
       </c>
       <c r="B15" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2032,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2060,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499104</v>
+        <v>499081</v>
       </c>
       <c r="R15" t="n">
-        <v>6820567</v>
+        <v>6820327</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486728</v>
+        <v>121486654</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2138,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499103</v>
+        <v>499174</v>
       </c>
       <c r="R16" t="n">
-        <v>6820567</v>
+        <v>6820509</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486586</v>
+        <v>121486711</v>
       </c>
       <c r="B17" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2240,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499101</v>
+        <v>499126</v>
       </c>
       <c r="R17" t="n">
-        <v>6820489</v>
+        <v>6820301</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486644</v>
+        <v>121486640</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,46 +2440,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499088</v>
+        <v>499110</v>
       </c>
       <c r="R19" t="n">
-        <v>6820326</v>
+        <v>6820446</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2510,7 +2512,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2529,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486611</v>
+        <v>121486744</v>
       </c>
       <c r="B20" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,25 +2542,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499075</v>
+        <v>499210</v>
       </c>
       <c r="R20" t="n">
-        <v>6820457</v>
+        <v>6820548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2632,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486714</v>
+        <v>121486728</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2671,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499120</v>
+        <v>499103</v>
       </c>
       <c r="R21" t="n">
-        <v>6820327</v>
+        <v>6820567</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,7 +2734,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486717</v>
+        <v>121486720</v>
       </c>
       <c r="B22" t="n">
         <v>78609</v>
@@ -2773,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499081</v>
+        <v>499064</v>
       </c>
       <c r="R22" t="n">
-        <v>6820327</v>
+        <v>6820411</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,10 +2836,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486748</v>
+        <v>121486643</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2851,21 +2852,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499224</v>
+        <v>499159</v>
       </c>
       <c r="R23" t="n">
-        <v>6820584</v>
+        <v>6820599</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2938,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486722</v>
+        <v>121486738</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -2977,10 +2978,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499063</v>
+        <v>499060</v>
       </c>
       <c r="R24" t="n">
-        <v>6820429</v>
+        <v>6820435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3040,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486729</v>
+        <v>121486719</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3079,10 +3080,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499121</v>
+        <v>499078</v>
       </c>
       <c r="R25" t="n">
-        <v>6820578</v>
+        <v>6820349</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,10 +3142,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486740</v>
+        <v>121486591</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3157,21 +3158,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3182,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499119</v>
+        <v>499060</v>
       </c>
       <c r="R26" t="n">
-        <v>6820450</v>
+        <v>6820434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,10 +3244,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486646</v>
+        <v>121486742</v>
       </c>
       <c r="B27" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3255,46 +3256,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499124</v>
+        <v>499140</v>
       </c>
       <c r="R27" t="n">
-        <v>6820580</v>
+        <v>6820485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,7 +3328,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3354,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486651</v>
+        <v>121486731</v>
       </c>
       <c r="B28" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3370,21 +3362,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3394,10 +3386,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499244</v>
+        <v>499150</v>
       </c>
       <c r="R28" t="n">
-        <v>6820418</v>
+        <v>6820595</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3456,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486643</v>
+        <v>121486729</v>
       </c>
       <c r="B29" t="n">
-        <v>80566</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3472,21 +3464,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3496,10 +3488,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499159</v>
+        <v>499121</v>
       </c>
       <c r="R29" t="n">
-        <v>6820599</v>
+        <v>6820578</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3558,10 +3550,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486766</v>
+        <v>121486649</v>
       </c>
       <c r="B30" t="n">
-        <v>78345</v>
+        <v>98105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3570,38 +3562,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499091</v>
+        <v>499099</v>
       </c>
       <c r="R30" t="n">
-        <v>6820459</v>
+        <v>6820449</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,6 +3642,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3660,7 +3661,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486710</v>
+        <v>121486743</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3700,10 +3701,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499134</v>
+        <v>499204</v>
       </c>
       <c r="R31" t="n">
-        <v>6820297</v>
+        <v>6820546</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,10 +3763,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486629</v>
+        <v>121486766</v>
       </c>
       <c r="B32" t="n">
-        <v>8435</v>
+        <v>78345</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3774,47 +3775,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499088</v>
+        <v>499091</v>
       </c>
       <c r="R32" t="n">
-        <v>6820469</v>
+        <v>6820459</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3855,7 +3847,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3874,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486711</v>
+        <v>121486623</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3890,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499126</v>
+        <v>499112</v>
       </c>
       <c r="R33" t="n">
-        <v>6820301</v>
+        <v>6820448</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3976,7 +3967,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486703</v>
+        <v>121486710</v>
       </c>
       <c r="B34" t="n">
         <v>78609</v>
@@ -4016,10 +4007,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499321</v>
+        <v>499134</v>
       </c>
       <c r="R34" t="n">
-        <v>6820523</v>
+        <v>6820297</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4078,10 +4069,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486652</v>
+        <v>121486718</v>
       </c>
       <c r="B35" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4094,21 +4085,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4118,10 +4109,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499247</v>
+        <v>499079</v>
       </c>
       <c r="R35" t="n">
-        <v>6820414</v>
+        <v>6820344</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,7 +4171,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486738</v>
+        <v>121486740</v>
       </c>
       <c r="B36" t="n">
         <v>78609</v>
@@ -4220,10 +4211,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499060</v>
+        <v>499119</v>
       </c>
       <c r="R36" t="n">
-        <v>6820435</v>
+        <v>6820450</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4282,10 +4273,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486640</v>
+        <v>121486721</v>
       </c>
       <c r="B37" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4298,21 +4289,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4322,10 +4313,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499110</v>
+        <v>499066</v>
       </c>
       <c r="R37" t="n">
-        <v>6820446</v>
+        <v>6820416</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,10 +4375,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486745</v>
+        <v>121486653</v>
       </c>
       <c r="B38" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4400,21 +4391,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4424,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499219</v>
+        <v>499063</v>
       </c>
       <c r="R38" t="n">
-        <v>6820563</v>
+        <v>6820418</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4486,10 +4477,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486730</v>
+        <v>121486626</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,25 +4489,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4526,10 +4517,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499159</v>
+        <v>499104</v>
       </c>
       <c r="R39" t="n">
-        <v>6820605</v>
+        <v>6820567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4588,10 +4579,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486712</v>
+        <v>121486637</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4604,21 +4595,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4628,10 +4619,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499123</v>
+        <v>499221</v>
       </c>
       <c r="R40" t="n">
-        <v>6820315</v>
+        <v>6820551</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4690,10 +4681,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486731</v>
+        <v>121486648</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4702,38 +4693,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499150</v>
+        <v>499087</v>
       </c>
       <c r="R41" t="n">
-        <v>6820595</v>
+        <v>6820462</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4774,6 +4773,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486636</v>
+        <v>121486628</v>
       </c>
       <c r="B42" t="n">
-        <v>78346</v>
+        <v>8435</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4804,38 +4804,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499244</v>
+        <v>499248</v>
       </c>
       <c r="R42" t="n">
-        <v>6820418</v>
+        <v>6820414</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,12 +4879,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4894,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486649</v>
+        <v>121486636</v>
       </c>
       <c r="B43" t="n">
-        <v>98105</v>
+        <v>78346</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4906,46 +4921,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499099</v>
+        <v>499244</v>
       </c>
       <c r="R43" t="n">
-        <v>6820449</v>
+        <v>6820418</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4986,7 +4993,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5005,10 +5011,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486713</v>
+        <v>121486641</v>
       </c>
       <c r="B44" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,21 +5027,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5045,10 +5051,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499123</v>
+        <v>499241</v>
       </c>
       <c r="R44" t="n">
-        <v>6820323</v>
+        <v>6820619</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5107,10 +5113,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486742</v>
+        <v>121486611</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5119,25 +5125,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5147,10 +5153,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499140</v>
+        <v>499075</v>
       </c>
       <c r="R45" t="n">
-        <v>6820485</v>
+        <v>6820457</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5209,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486718</v>
+        <v>121486644</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5221,38 +5227,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499079</v>
+        <v>499088</v>
       </c>
       <c r="R46" t="n">
-        <v>6820344</v>
+        <v>6820326</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5293,6 +5307,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5311,10 +5326,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486612</v>
+        <v>121486748</v>
       </c>
       <c r="B47" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5323,25 +5338,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5351,10 +5366,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499163</v>
+        <v>499224</v>
       </c>
       <c r="R47" t="n">
-        <v>6820511</v>
+        <v>6820584</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5413,10 +5428,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486628</v>
+        <v>121486586</v>
       </c>
       <c r="B48" t="n">
-        <v>8435</v>
+        <v>79227</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5425,47 +5440,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499248</v>
+        <v>499101</v>
       </c>
       <c r="R48" t="n">
-        <v>6820414</v>
+        <v>6820489</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5500,18 +5506,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486591</v>
+        <v>121486722</v>
       </c>
       <c r="B49" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499060</v>
+        <v>499063</v>
       </c>
       <c r="R49" t="n">
-        <v>6820434</v>
+        <v>6820429</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486641</v>
+        <v>121486635</v>
       </c>
       <c r="B50" t="n">
-        <v>79690</v>
+        <v>78346</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499241</v>
+        <v>499279</v>
       </c>
       <c r="R50" t="n">
-        <v>6820619</v>
+        <v>6820470</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486654</v>
+        <v>121486713</v>
       </c>
       <c r="B51" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499174</v>
+        <v>499123</v>
       </c>
       <c r="R51" t="n">
-        <v>6820509</v>
+        <v>6820323</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486653</v>
+        <v>121486712</v>
       </c>
       <c r="B52" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499063</v>
+        <v>499123</v>
       </c>
       <c r="R52" t="n">
-        <v>6820418</v>
+        <v>6820315</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486714</v>
+        <v>121486658</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499120</v>
+        <v>499221</v>
       </c>
       <c r="R2" t="n">
-        <v>6820327</v>
+        <v>6820551</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486612</v>
+        <v>121486592</v>
       </c>
       <c r="B3" t="n">
-        <v>79719</v>
+        <v>74715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499163</v>
+        <v>499180</v>
       </c>
       <c r="R3" t="n">
-        <v>6820511</v>
+        <v>6820509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486592</v>
+        <v>121486611</v>
       </c>
       <c r="B4" t="n">
-        <v>74715</v>
+        <v>79719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499180</v>
+        <v>499075</v>
       </c>
       <c r="R4" t="n">
-        <v>6820509</v>
+        <v>6820457</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486652</v>
+        <v>121486712</v>
       </c>
       <c r="B5" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499247</v>
+        <v>499123</v>
       </c>
       <c r="R5" t="n">
-        <v>6820414</v>
+        <v>6820315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486646</v>
+        <v>121486738</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,46 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499124</v>
+        <v>499060</v>
       </c>
       <c r="R6" t="n">
-        <v>6820580</v>
+        <v>6820435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1194,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486587</v>
+        <v>121486718</v>
       </c>
       <c r="B7" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499137</v>
+        <v>499079</v>
       </c>
       <c r="R7" t="n">
-        <v>6820469</v>
+        <v>6820344</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486730</v>
+        <v>121486748</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499159</v>
+        <v>499224</v>
       </c>
       <c r="R8" t="n">
-        <v>6820605</v>
+        <v>6820584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486745</v>
+        <v>121486719</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1438,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499219</v>
+        <v>499078</v>
       </c>
       <c r="R9" t="n">
-        <v>6820563</v>
+        <v>6820349</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486658</v>
+        <v>121486728</v>
       </c>
       <c r="B10" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499221</v>
+        <v>499103</v>
       </c>
       <c r="R10" t="n">
-        <v>6820551</v>
+        <v>6820567</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486703</v>
+        <v>121486651</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499321</v>
+        <v>499244</v>
       </c>
       <c r="R11" t="n">
-        <v>6820523</v>
+        <v>6820418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486629</v>
+        <v>121486729</v>
       </c>
       <c r="B12" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,47 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499088</v>
+        <v>499121</v>
       </c>
       <c r="R12" t="n">
-        <v>6820469</v>
+        <v>6820578</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1779,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1816,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486715</v>
+        <v>121486649</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,38 +1809,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499085</v>
+        <v>499099</v>
       </c>
       <c r="R13" t="n">
-        <v>6820324</v>
+        <v>6820449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,6 +1889,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1918,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486651</v>
+        <v>121486740</v>
       </c>
       <c r="B14" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499244</v>
+        <v>499119</v>
       </c>
       <c r="R14" t="n">
-        <v>6820418</v>
+        <v>6820450</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486717</v>
+        <v>121486641</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2060,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499081</v>
+        <v>499241</v>
       </c>
       <c r="R15" t="n">
-        <v>6820327</v>
+        <v>6820619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486654</v>
+        <v>121486715</v>
       </c>
       <c r="B16" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2162,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499174</v>
+        <v>499085</v>
       </c>
       <c r="R16" t="n">
-        <v>6820509</v>
+        <v>6820324</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486711</v>
+        <v>121486731</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2264,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499126</v>
+        <v>499150</v>
       </c>
       <c r="R17" t="n">
-        <v>6820301</v>
+        <v>6820595</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486739</v>
+        <v>121486626</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499079</v>
+        <v>499104</v>
       </c>
       <c r="R18" t="n">
-        <v>6820445</v>
+        <v>6820567</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486640</v>
+        <v>121486730</v>
       </c>
       <c r="B19" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499110</v>
+        <v>499159</v>
       </c>
       <c r="R19" t="n">
-        <v>6820446</v>
+        <v>6820605</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486744</v>
+        <v>121486587</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499210</v>
+        <v>499137</v>
       </c>
       <c r="R20" t="n">
-        <v>6820548</v>
+        <v>6820469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486728</v>
+        <v>121486591</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2648,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499103</v>
+        <v>499060</v>
       </c>
       <c r="R21" t="n">
-        <v>6820567</v>
+        <v>6820434</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486720</v>
+        <v>121486648</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,38 +2736,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499064</v>
+        <v>499087</v>
       </c>
       <c r="R22" t="n">
-        <v>6820411</v>
+        <v>6820462</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,6 +2816,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2836,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486643</v>
+        <v>121486612</v>
       </c>
       <c r="B23" t="n">
-        <v>80566</v>
+        <v>79719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,25 +2847,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499159</v>
+        <v>499163</v>
       </c>
       <c r="R23" t="n">
-        <v>6820599</v>
+        <v>6820511</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,7 +2937,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486738</v>
+        <v>121486739</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -2978,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499060</v>
+        <v>499079</v>
       </c>
       <c r="R24" t="n">
-        <v>6820435</v>
+        <v>6820445</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3040,7 +3039,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486719</v>
+        <v>121486711</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3080,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499078</v>
+        <v>499126</v>
       </c>
       <c r="R25" t="n">
-        <v>6820349</v>
+        <v>6820301</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486591</v>
+        <v>121486722</v>
       </c>
       <c r="B26" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3158,21 +3157,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3182,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499060</v>
+        <v>499063</v>
       </c>
       <c r="R26" t="n">
-        <v>6820434</v>
+        <v>6820429</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3346,7 +3345,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486731</v>
+        <v>121486710</v>
       </c>
       <c r="B28" t="n">
         <v>78609</v>
@@ -3386,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499150</v>
+        <v>499134</v>
       </c>
       <c r="R28" t="n">
-        <v>6820595</v>
+        <v>6820297</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486729</v>
+        <v>121486646</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3460,38 +3459,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499121</v>
+        <v>499124</v>
       </c>
       <c r="R29" t="n">
-        <v>6820578</v>
+        <v>6820580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3532,6 +3539,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3550,10 +3558,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486649</v>
+        <v>121486636</v>
       </c>
       <c r="B30" t="n">
-        <v>98105</v>
+        <v>78346</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3562,46 +3570,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499099</v>
+        <v>499244</v>
       </c>
       <c r="R30" t="n">
-        <v>6820449</v>
+        <v>6820418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,7 +3642,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3661,10 +3660,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486743</v>
+        <v>121486628</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,38 +3672,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499204</v>
+        <v>499248</v>
       </c>
       <c r="R31" t="n">
-        <v>6820546</v>
+        <v>6820414</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,12 +3747,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3763,10 +3777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486766</v>
+        <v>121486717</v>
       </c>
       <c r="B32" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3779,21 +3793,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3803,10 +3817,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499091</v>
+        <v>499081</v>
       </c>
       <c r="R32" t="n">
-        <v>6820459</v>
+        <v>6820327</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3865,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486623</v>
+        <v>121486745</v>
       </c>
       <c r="B33" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3881,21 +3895,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3919,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499112</v>
+        <v>499219</v>
       </c>
       <c r="R33" t="n">
-        <v>6820448</v>
+        <v>6820563</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3981,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486710</v>
+        <v>121486635</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3983,21 +3997,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4007,10 +4021,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499134</v>
+        <v>499279</v>
       </c>
       <c r="R34" t="n">
-        <v>6820297</v>
+        <v>6820470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4069,7 +4083,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486718</v>
+        <v>121486703</v>
       </c>
       <c r="B35" t="n">
         <v>78609</v>
@@ -4109,10 +4123,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499079</v>
+        <v>499321</v>
       </c>
       <c r="R35" t="n">
-        <v>6820344</v>
+        <v>6820523</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4171,10 +4185,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486740</v>
+        <v>121486643</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4187,21 +4201,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4211,10 +4225,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499119</v>
+        <v>499159</v>
       </c>
       <c r="R36" t="n">
-        <v>6820450</v>
+        <v>6820599</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4273,10 +4287,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486721</v>
+        <v>121486640</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4289,21 +4303,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4313,10 +4327,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499066</v>
+        <v>499110</v>
       </c>
       <c r="R37" t="n">
-        <v>6820416</v>
+        <v>6820446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4375,10 +4389,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486653</v>
+        <v>121486644</v>
       </c>
       <c r="B38" t="n">
-        <v>78345</v>
+        <v>98105</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,38 +4401,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499063</v>
+        <v>499088</v>
       </c>
       <c r="R38" t="n">
-        <v>6820418</v>
+        <v>6820326</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,6 +4481,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4477,10 +4500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486626</v>
+        <v>121486623</v>
       </c>
       <c r="B39" t="n">
-        <v>97059</v>
+        <v>79691</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4489,25 +4512,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4517,10 +4540,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499104</v>
+        <v>499112</v>
       </c>
       <c r="R39" t="n">
-        <v>6820567</v>
+        <v>6820448</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,10 +4602,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486637</v>
+        <v>121486586</v>
       </c>
       <c r="B40" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4595,21 +4618,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4619,10 +4642,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499221</v>
+        <v>499101</v>
       </c>
       <c r="R40" t="n">
-        <v>6820551</v>
+        <v>6820489</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4681,10 +4704,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486648</v>
+        <v>121486654</v>
       </c>
       <c r="B41" t="n">
-        <v>98105</v>
+        <v>78345</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4693,46 +4716,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499087</v>
+        <v>499174</v>
       </c>
       <c r="R41" t="n">
-        <v>6820462</v>
+        <v>6820509</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4773,7 +4788,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4792,10 +4806,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486628</v>
+        <v>121486743</v>
       </c>
       <c r="B42" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4804,47 +4818,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499248</v>
+        <v>499204</v>
       </c>
       <c r="R42" t="n">
-        <v>6820414</v>
+        <v>6820546</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,18 +4884,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4909,10 +4908,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486636</v>
+        <v>121486744</v>
       </c>
       <c r="B43" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4925,21 +4924,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4948,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499244</v>
+        <v>499210</v>
       </c>
       <c r="R43" t="n">
-        <v>6820418</v>
+        <v>6820548</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5011,10 +5010,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486641</v>
+        <v>121486720</v>
       </c>
       <c r="B44" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5027,21 +5026,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5051,10 +5050,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499241</v>
+        <v>499064</v>
       </c>
       <c r="R44" t="n">
-        <v>6820619</v>
+        <v>6820411</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5113,10 +5112,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486611</v>
+        <v>121486713</v>
       </c>
       <c r="B45" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5125,25 +5124,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5153,10 +5152,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499075</v>
+        <v>499123</v>
       </c>
       <c r="R45" t="n">
-        <v>6820457</v>
+        <v>6820323</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,10 +5214,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486644</v>
+        <v>121486653</v>
       </c>
       <c r="B46" t="n">
-        <v>98105</v>
+        <v>78345</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5227,46 +5226,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499088</v>
+        <v>499063</v>
       </c>
       <c r="R46" t="n">
-        <v>6820326</v>
+        <v>6820418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5307,7 +5298,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5326,10 +5316,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486748</v>
+        <v>121486652</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5342,21 +5332,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5366,10 +5356,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499224</v>
+        <v>499247</v>
       </c>
       <c r="R47" t="n">
-        <v>6820584</v>
+        <v>6820414</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5428,10 +5418,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486586</v>
+        <v>121486629</v>
       </c>
       <c r="B48" t="n">
-        <v>79227</v>
+        <v>8435</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5440,38 +5430,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499101</v>
+        <v>499088</v>
       </c>
       <c r="R48" t="n">
-        <v>6820489</v>
+        <v>6820469</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5512,6 +5511,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486722</v>
+        <v>121486637</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499063</v>
+        <v>499221</v>
       </c>
       <c r="R49" t="n">
-        <v>6820429</v>
+        <v>6820551</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486635</v>
+        <v>121486714</v>
       </c>
       <c r="B50" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499279</v>
+        <v>499120</v>
       </c>
       <c r="R50" t="n">
-        <v>6820470</v>
+        <v>6820327</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486713</v>
+        <v>121486721</v>
       </c>
       <c r="B51" t="n">
         <v>78609</v>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499123</v>
+        <v>499066</v>
       </c>
       <c r="R51" t="n">
-        <v>6820323</v>
+        <v>6820416</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486712</v>
+        <v>121486766</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499123</v>
+        <v>499091</v>
       </c>
       <c r="R52" t="n">
-        <v>6820315</v>
+        <v>6820459</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121475595</v>
+        <v>121475875</v>
       </c>
       <c r="B53" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5954,34 +5954,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
+          <t>Långtallarna, Långtallarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499216</v>
+        <v>499095</v>
       </c>
       <c r="R53" t="n">
-        <v>6820553</v>
+        <v>6820473</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6050,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121475875</v>
+        <v>121475595</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6066,34 +6066,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långtallarna, Långtallarna, Dlr</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499095</v>
+        <v>499216</v>
       </c>
       <c r="R54" t="n">
-        <v>6820473</v>
+        <v>6820553</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486658</v>
+        <v>121486739</v>
       </c>
       <c r="B2" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499221</v>
+        <v>499079</v>
       </c>
       <c r="R2" t="n">
-        <v>6820551</v>
+        <v>6820445</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486592</v>
+        <v>121486711</v>
       </c>
       <c r="B3" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499180</v>
+        <v>499126</v>
       </c>
       <c r="R3" t="n">
-        <v>6820509</v>
+        <v>6820301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486611</v>
+        <v>121486722</v>
       </c>
       <c r="B4" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499075</v>
+        <v>499063</v>
       </c>
       <c r="R4" t="n">
-        <v>6820457</v>
+        <v>6820429</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486712</v>
+        <v>121486717</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499123</v>
+        <v>499081</v>
       </c>
       <c r="R5" t="n">
-        <v>6820315</v>
+        <v>6820327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486738</v>
+        <v>121486587</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499060</v>
+        <v>499137</v>
       </c>
       <c r="R6" t="n">
-        <v>6820435</v>
+        <v>6820469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486718</v>
+        <v>121486740</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499079</v>
+        <v>499119</v>
       </c>
       <c r="R7" t="n">
-        <v>6820344</v>
+        <v>6820450</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486748</v>
+        <v>121486644</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499224</v>
+        <v>499088</v>
       </c>
       <c r="R8" t="n">
-        <v>6820584</v>
+        <v>6820326</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1379,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486719</v>
+        <v>121486742</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1429,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499078</v>
+        <v>499140</v>
       </c>
       <c r="R9" t="n">
-        <v>6820349</v>
+        <v>6820485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486728</v>
+        <v>121486591</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499103</v>
+        <v>499060</v>
       </c>
       <c r="R10" t="n">
-        <v>6820567</v>
+        <v>6820434</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486651</v>
+        <v>121486718</v>
       </c>
       <c r="B11" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499244</v>
+        <v>499079</v>
       </c>
       <c r="R11" t="n">
-        <v>6820418</v>
+        <v>6820344</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486729</v>
+        <v>121486720</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1735,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499121</v>
+        <v>499064</v>
       </c>
       <c r="R12" t="n">
-        <v>6820578</v>
+        <v>6820411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486649</v>
+        <v>121486648</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1845,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499099</v>
+        <v>499087</v>
       </c>
       <c r="R13" t="n">
-        <v>6820449</v>
+        <v>6820462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486740</v>
+        <v>121486654</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1933,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499119</v>
+        <v>499174</v>
       </c>
       <c r="R14" t="n">
-        <v>6820450</v>
+        <v>6820509</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486641</v>
+        <v>121486651</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2035,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499241</v>
+        <v>499244</v>
       </c>
       <c r="R15" t="n">
-        <v>6820619</v>
+        <v>6820418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486715</v>
+        <v>121486635</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2137,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499085</v>
+        <v>499279</v>
       </c>
       <c r="R16" t="n">
-        <v>6820324</v>
+        <v>6820470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,7 +2223,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486731</v>
+        <v>121486721</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2254,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499150</v>
+        <v>499066</v>
       </c>
       <c r="R17" t="n">
-        <v>6820595</v>
+        <v>6820416</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486626</v>
+        <v>121486710</v>
       </c>
       <c r="B18" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2337,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499104</v>
+        <v>499134</v>
       </c>
       <c r="R18" t="n">
-        <v>6820567</v>
+        <v>6820297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486730</v>
+        <v>121486629</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,38 +2439,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499159</v>
+        <v>499088</v>
       </c>
       <c r="R19" t="n">
-        <v>6820605</v>
+        <v>6820469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,6 +2520,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2520,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486587</v>
+        <v>121486715</v>
       </c>
       <c r="B20" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499137</v>
+        <v>499085</v>
       </c>
       <c r="R20" t="n">
-        <v>6820469</v>
+        <v>6820324</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486591</v>
+        <v>121486744</v>
       </c>
       <c r="B21" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499060</v>
+        <v>499210</v>
       </c>
       <c r="R21" t="n">
-        <v>6820434</v>
+        <v>6820548</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486648</v>
+        <v>121486714</v>
       </c>
       <c r="B22" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,46 +2755,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499087</v>
+        <v>499120</v>
       </c>
       <c r="R22" t="n">
-        <v>6820462</v>
+        <v>6820327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,7 +2827,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2835,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486612</v>
+        <v>121486719</v>
       </c>
       <c r="B23" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2847,25 +2857,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499163</v>
+        <v>499078</v>
       </c>
       <c r="R23" t="n">
-        <v>6820511</v>
+        <v>6820349</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486739</v>
+        <v>121486658</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,21 +2963,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499079</v>
+        <v>499221</v>
       </c>
       <c r="R24" t="n">
-        <v>6820445</v>
+        <v>6820551</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486711</v>
+        <v>121486643</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>80566</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3055,21 +3065,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499126</v>
+        <v>499159</v>
       </c>
       <c r="R25" t="n">
-        <v>6820301</v>
+        <v>6820599</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3151,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486722</v>
+        <v>121486745</v>
       </c>
       <c r="B26" t="n">
         <v>78609</v>
@@ -3181,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499063</v>
+        <v>499219</v>
       </c>
       <c r="R26" t="n">
-        <v>6820429</v>
+        <v>6820563</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486742</v>
+        <v>121486641</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3259,21 +3269,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3283,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499140</v>
+        <v>499241</v>
       </c>
       <c r="R27" t="n">
-        <v>6820485</v>
+        <v>6820619</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,10 +3355,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486710</v>
+        <v>121486592</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3361,21 +3371,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,10 +3395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499134</v>
+        <v>499180</v>
       </c>
       <c r="R28" t="n">
-        <v>6820297</v>
+        <v>6820509</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3447,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486646</v>
+        <v>121486766</v>
       </c>
       <c r="B29" t="n">
-        <v>98105</v>
+        <v>78345</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3459,46 +3469,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499124</v>
+        <v>499091</v>
       </c>
       <c r="R29" t="n">
-        <v>6820580</v>
+        <v>6820459</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,7 +3541,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3559,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486636</v>
+        <v>121486703</v>
       </c>
       <c r="B30" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3574,21 +3575,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3598,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499244</v>
+        <v>499321</v>
       </c>
       <c r="R30" t="n">
-        <v>6820418</v>
+        <v>6820523</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3660,10 +3661,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486628</v>
+        <v>121486612</v>
       </c>
       <c r="B31" t="n">
-        <v>8435</v>
+        <v>79719</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3676,43 +3677,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499248</v>
+        <v>499163</v>
       </c>
       <c r="R31" t="n">
-        <v>6820414</v>
+        <v>6820511</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,18 +3739,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3777,10 +3763,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486717</v>
+        <v>121486611</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3789,25 +3775,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3817,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499081</v>
+        <v>499075</v>
       </c>
       <c r="R32" t="n">
-        <v>6820327</v>
+        <v>6820457</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3879,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486745</v>
+        <v>121486640</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3895,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3919,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499219</v>
+        <v>499110</v>
       </c>
       <c r="R33" t="n">
-        <v>6820563</v>
+        <v>6820446</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3981,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486635</v>
+        <v>121486623</v>
       </c>
       <c r="B34" t="n">
-        <v>78346</v>
+        <v>79691</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3997,21 +3983,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4021,10 +4007,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499279</v>
+        <v>499112</v>
       </c>
       <c r="R34" t="n">
-        <v>6820470</v>
+        <v>6820448</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4083,10 +4069,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486703</v>
+        <v>121486646</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4095,38 +4081,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499321</v>
+        <v>499124</v>
       </c>
       <c r="R35" t="n">
-        <v>6820523</v>
+        <v>6820580</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,6 +4161,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4185,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486643</v>
+        <v>121486712</v>
       </c>
       <c r="B36" t="n">
-        <v>80566</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4201,21 +4196,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499159</v>
+        <v>499123</v>
       </c>
       <c r="R36" t="n">
-        <v>6820599</v>
+        <v>6820315</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4287,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486640</v>
+        <v>121486637</v>
       </c>
       <c r="B37" t="n">
-        <v>79690</v>
+        <v>78346</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4303,21 +4298,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4327,10 +4322,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499110</v>
+        <v>499221</v>
       </c>
       <c r="R37" t="n">
-        <v>6820446</v>
+        <v>6820551</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4389,10 +4384,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486644</v>
+        <v>121486628</v>
       </c>
       <c r="B38" t="n">
-        <v>98105</v>
+        <v>8435</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4401,35 +4396,36 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4437,10 +4433,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499088</v>
+        <v>499248</v>
       </c>
       <c r="R38" t="n">
-        <v>6820326</v>
+        <v>6820414</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,6 +4469,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4500,10 +4501,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486623</v>
+        <v>121486626</v>
       </c>
       <c r="B39" t="n">
-        <v>79691</v>
+        <v>97059</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4512,25 +4513,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4540,10 +4541,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499112</v>
+        <v>499104</v>
       </c>
       <c r="R39" t="n">
-        <v>6820448</v>
+        <v>6820567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4602,10 +4603,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486586</v>
+        <v>121486738</v>
       </c>
       <c r="B40" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4618,21 +4619,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4642,10 +4643,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499101</v>
+        <v>499060</v>
       </c>
       <c r="R40" t="n">
-        <v>6820489</v>
+        <v>6820435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,10 +4705,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486654</v>
+        <v>121486731</v>
       </c>
       <c r="B41" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4720,21 +4721,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4744,10 +4745,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499174</v>
+        <v>499150</v>
       </c>
       <c r="R41" t="n">
-        <v>6820509</v>
+        <v>6820595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4806,7 +4807,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486743</v>
+        <v>121486730</v>
       </c>
       <c r="B42" t="n">
         <v>78609</v>
@@ -4846,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499204</v>
+        <v>499159</v>
       </c>
       <c r="R42" t="n">
-        <v>6820546</v>
+        <v>6820605</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4908,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486744</v>
+        <v>121486649</v>
       </c>
       <c r="B43" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4920,38 +4921,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499210</v>
+        <v>499099</v>
       </c>
       <c r="R43" t="n">
-        <v>6820548</v>
+        <v>6820449</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,6 +5001,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5010,7 +5020,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486720</v>
+        <v>121486743</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -5050,10 +5060,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499064</v>
+        <v>499204</v>
       </c>
       <c r="R44" t="n">
-        <v>6820411</v>
+        <v>6820546</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5112,7 +5122,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486713</v>
+        <v>121486748</v>
       </c>
       <c r="B45" t="n">
         <v>78609</v>
@@ -5152,10 +5162,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499123</v>
+        <v>499224</v>
       </c>
       <c r="R45" t="n">
-        <v>6820323</v>
+        <v>6820584</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5214,10 +5224,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486653</v>
+        <v>121486636</v>
       </c>
       <c r="B46" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5230,21 +5240,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5254,7 +5264,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499063</v>
+        <v>499244</v>
       </c>
       <c r="R46" t="n">
         <v>6820418</v>
@@ -5316,10 +5326,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486652</v>
+        <v>121486729</v>
       </c>
       <c r="B47" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5332,21 +5342,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5356,10 +5366,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499247</v>
+        <v>499121</v>
       </c>
       <c r="R47" t="n">
-        <v>6820414</v>
+        <v>6820578</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5418,10 +5428,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486629</v>
+        <v>121486652</v>
       </c>
       <c r="B48" t="n">
-        <v>8435</v>
+        <v>78345</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5430,47 +5440,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499088</v>
+        <v>499247</v>
       </c>
       <c r="R48" t="n">
-        <v>6820469</v>
+        <v>6820414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5511,7 +5512,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486637</v>
+        <v>121486713</v>
       </c>
       <c r="B49" t="n">
-        <v>78346</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499221</v>
+        <v>499123</v>
       </c>
       <c r="R49" t="n">
-        <v>6820551</v>
+        <v>6820323</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486714</v>
+        <v>121486653</v>
       </c>
       <c r="B50" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,21 +5648,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499120</v>
+        <v>499063</v>
       </c>
       <c r="R50" t="n">
-        <v>6820327</v>
+        <v>6820418</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486721</v>
+        <v>121486728</v>
       </c>
       <c r="B51" t="n">
         <v>78609</v>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499066</v>
+        <v>499103</v>
       </c>
       <c r="R51" t="n">
-        <v>6820416</v>
+        <v>6820567</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486766</v>
+        <v>121486586</v>
       </c>
       <c r="B52" t="n">
-        <v>78345</v>
+        <v>79227</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499091</v>
+        <v>499101</v>
       </c>
       <c r="R52" t="n">
-        <v>6820459</v>
+        <v>6820489</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121475875</v>
+        <v>121475595</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5954,34 +5954,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långtallarna, Långtallarna, Dlr</t>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499095</v>
+        <v>499216</v>
       </c>
       <c r="R53" t="n">
-        <v>6820473</v>
+        <v>6820553</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6050,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121475595</v>
+        <v>121475875</v>
       </c>
       <c r="B54" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6066,34 +6066,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
+          <t>Långtallarna, Långtallarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499216</v>
+        <v>499095</v>
       </c>
       <c r="R54" t="n">
-        <v>6820553</v>
+        <v>6820473</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486587</v>
+        <v>121486644</v>
       </c>
       <c r="B6" t="n">
-        <v>79227</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499137</v>
+        <v>499088</v>
       </c>
       <c r="R6" t="n">
-        <v>6820469</v>
+        <v>6820326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1175,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486644</v>
+        <v>121486587</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>79227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,46 +1308,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499088</v>
+        <v>499137</v>
       </c>
       <c r="R8" t="n">
-        <v>6820326</v>
+        <v>6820469</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,7 +1380,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486623</v>
+        <v>121486646</v>
       </c>
       <c r="B34" t="n">
-        <v>79691</v>
+        <v>98105</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3979,38 +3979,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499112</v>
+        <v>499124</v>
       </c>
       <c r="R34" t="n">
-        <v>6820448</v>
+        <v>6820580</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,6 +4059,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4069,10 +4078,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486646</v>
+        <v>121486637</v>
       </c>
       <c r="B35" t="n">
-        <v>98105</v>
+        <v>78346</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,46 +4090,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499124</v>
+        <v>499221</v>
       </c>
       <c r="R35" t="n">
-        <v>6820580</v>
+        <v>6820551</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4161,7 +4162,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486637</v>
+        <v>121486623</v>
       </c>
       <c r="B37" t="n">
-        <v>78346</v>
+        <v>79691</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4298,21 +4298,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499221</v>
+        <v>499112</v>
       </c>
       <c r="R37" t="n">
-        <v>6820551</v>
+        <v>6820448</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,10 +4384,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486628</v>
+        <v>121486738</v>
       </c>
       <c r="B38" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4396,47 +4396,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499248</v>
+        <v>499060</v>
       </c>
       <c r="R38" t="n">
-        <v>6820414</v>
+        <v>6820435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,18 +4462,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4501,10 +4486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486626</v>
+        <v>121486731</v>
       </c>
       <c r="B39" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4513,25 +4498,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4541,10 +4526,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499104</v>
+        <v>499150</v>
       </c>
       <c r="R39" t="n">
-        <v>6820567</v>
+        <v>6820595</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4603,7 +4588,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486738</v>
+        <v>121486730</v>
       </c>
       <c r="B40" t="n">
         <v>78609</v>
@@ -4643,10 +4628,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499060</v>
+        <v>499159</v>
       </c>
       <c r="R40" t="n">
-        <v>6820435</v>
+        <v>6820605</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4705,10 +4690,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486731</v>
+        <v>121486628</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4717,38 +4702,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499150</v>
+        <v>499248</v>
       </c>
       <c r="R41" t="n">
-        <v>6820595</v>
+        <v>6820414</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4783,12 +4777,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486730</v>
+        <v>121486626</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4819,25 +4819,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499159</v>
+        <v>499104</v>
       </c>
       <c r="R42" t="n">
-        <v>6820605</v>
+        <v>6820567</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -4180,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486712</v>
+        <v>121486623</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499123</v>
+        <v>499112</v>
       </c>
       <c r="R36" t="n">
-        <v>6820315</v>
+        <v>6820448</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4282,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486623</v>
+        <v>121486712</v>
       </c>
       <c r="B37" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4298,21 +4298,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499112</v>
+        <v>499123</v>
       </c>
       <c r="R37" t="n">
-        <v>6820448</v>
+        <v>6820315</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,10 +4384,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486738</v>
+        <v>121486628</v>
       </c>
       <c r="B38" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4396,38 +4396,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499060</v>
+        <v>499248</v>
       </c>
       <c r="R38" t="n">
-        <v>6820435</v>
+        <v>6820414</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4462,12 +4471,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4486,10 +4501,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486731</v>
+        <v>121486626</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,25 +4513,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4526,10 +4541,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499150</v>
+        <v>499104</v>
       </c>
       <c r="R39" t="n">
-        <v>6820595</v>
+        <v>6820567</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4588,7 +4603,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486730</v>
+        <v>121486738</v>
       </c>
       <c r="B40" t="n">
         <v>78609</v>
@@ -4628,10 +4643,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499159</v>
+        <v>499060</v>
       </c>
       <c r="R40" t="n">
-        <v>6820605</v>
+        <v>6820435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4690,10 +4705,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486628</v>
+        <v>121486731</v>
       </c>
       <c r="B41" t="n">
-        <v>8435</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4702,47 +4717,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499248</v>
+        <v>499150</v>
       </c>
       <c r="R41" t="n">
-        <v>6820414</v>
+        <v>6820595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4777,18 +4783,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486626</v>
+        <v>121486730</v>
       </c>
       <c r="B42" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4819,25 +4819,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499104</v>
+        <v>499159</v>
       </c>
       <c r="R42" t="n">
-        <v>6820567</v>
+        <v>6820605</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486739</v>
+        <v>121486722</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499079</v>
+        <v>499063</v>
       </c>
       <c r="R2" t="n">
-        <v>6820445</v>
+        <v>6820429</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486711</v>
+        <v>121486652</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499126</v>
+        <v>499247</v>
       </c>
       <c r="R3" t="n">
-        <v>6820301</v>
+        <v>6820414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486722</v>
+        <v>121486718</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499063</v>
+        <v>499079</v>
       </c>
       <c r="R4" t="n">
-        <v>6820429</v>
+        <v>6820344</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486717</v>
+        <v>121486636</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78353</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499081</v>
+        <v>499244</v>
       </c>
       <c r="R5" t="n">
-        <v>6820327</v>
+        <v>6820418</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486644</v>
+        <v>121486635</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>78353</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,46 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499088</v>
+        <v>499279</v>
       </c>
       <c r="R6" t="n">
-        <v>6820326</v>
+        <v>6820470</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1194,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486740</v>
+        <v>121486649</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,38 +1197,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499119</v>
+        <v>499099</v>
       </c>
       <c r="R7" t="n">
-        <v>6820450</v>
+        <v>6820449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,6 +1277,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486587</v>
+        <v>121486654</v>
       </c>
       <c r="B8" t="n">
-        <v>79227</v>
+        <v>78352</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499137</v>
+        <v>499174</v>
       </c>
       <c r="R8" t="n">
-        <v>6820469</v>
+        <v>6820509</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486742</v>
+        <v>121486703</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499140</v>
+        <v>499321</v>
       </c>
       <c r="R9" t="n">
-        <v>6820485</v>
+        <v>6820523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486591</v>
+        <v>121486587</v>
       </c>
       <c r="B10" t="n">
-        <v>74715</v>
+        <v>79234</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499060</v>
+        <v>499137</v>
       </c>
       <c r="R10" t="n">
-        <v>6820434</v>
+        <v>6820469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486718</v>
+        <v>121486730</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499079</v>
+        <v>499159</v>
       </c>
       <c r="R11" t="n">
-        <v>6820344</v>
+        <v>6820605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486720</v>
+        <v>121486640</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499064</v>
+        <v>499110</v>
       </c>
       <c r="R12" t="n">
-        <v>6820411</v>
+        <v>6820446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486648</v>
+        <v>121486612</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>79726</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,46 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499087</v>
+        <v>499163</v>
       </c>
       <c r="R13" t="n">
-        <v>6820462</v>
+        <v>6820511</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1890,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1917,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486654</v>
+        <v>121486641</v>
       </c>
       <c r="B14" t="n">
-        <v>78345</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499174</v>
+        <v>499241</v>
       </c>
       <c r="R14" t="n">
-        <v>6820509</v>
+        <v>6820619</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486651</v>
+        <v>121486720</v>
       </c>
       <c r="B15" t="n">
-        <v>78345</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499244</v>
+        <v>499064</v>
       </c>
       <c r="R15" t="n">
-        <v>6820418</v>
+        <v>6820411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486635</v>
+        <v>121486742</v>
       </c>
       <c r="B16" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2137,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2161,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499279</v>
+        <v>499140</v>
       </c>
       <c r="R16" t="n">
-        <v>6820470</v>
+        <v>6820485</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486721</v>
+        <v>121486744</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499066</v>
+        <v>499210</v>
       </c>
       <c r="R17" t="n">
-        <v>6820416</v>
+        <v>6820548</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486710</v>
+        <v>121486729</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499134</v>
+        <v>499121</v>
       </c>
       <c r="R18" t="n">
-        <v>6820297</v>
+        <v>6820578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486629</v>
+        <v>121486717</v>
       </c>
       <c r="B19" t="n">
-        <v>8435</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,47 +2430,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499088</v>
+        <v>499081</v>
       </c>
       <c r="R19" t="n">
-        <v>6820469</v>
+        <v>6820327</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,7 +2502,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2539,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486715</v>
+        <v>121486653</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2555,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499085</v>
+        <v>499063</v>
       </c>
       <c r="R20" t="n">
-        <v>6820324</v>
+        <v>6820418</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486744</v>
+        <v>121486611</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499210</v>
+        <v>499075</v>
       </c>
       <c r="R21" t="n">
-        <v>6820548</v>
+        <v>6820457</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2743,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486714</v>
+        <v>121486628</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>8436</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,38 +2736,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499120</v>
+        <v>499248</v>
       </c>
       <c r="R22" t="n">
-        <v>6820327</v>
+        <v>6820414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,12 +2811,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2845,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486719</v>
+        <v>121486648</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,38 +2853,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499078</v>
+        <v>499087</v>
       </c>
       <c r="R23" t="n">
-        <v>6820349</v>
+        <v>6820462</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,6 +2933,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2947,10 +2952,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486658</v>
+        <v>121486714</v>
       </c>
       <c r="B24" t="n">
-        <v>78345</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2963,21 +2968,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499221</v>
+        <v>499120</v>
       </c>
       <c r="R24" t="n">
-        <v>6820551</v>
+        <v>6820327</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3049,10 +3054,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486643</v>
+        <v>121486646</v>
       </c>
       <c r="B25" t="n">
-        <v>80566</v>
+        <v>98113</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,38 +3066,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499159</v>
+        <v>499124</v>
       </c>
       <c r="R25" t="n">
-        <v>6820599</v>
+        <v>6820580</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,6 +3146,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3151,10 +3165,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486745</v>
+        <v>121486637</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>78353</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,21 +3181,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3205,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499219</v>
+        <v>499221</v>
       </c>
       <c r="R26" t="n">
-        <v>6820563</v>
+        <v>6820551</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,10 +3267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486641</v>
+        <v>121486623</v>
       </c>
       <c r="B27" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3269,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499241</v>
+        <v>499112</v>
       </c>
       <c r="R27" t="n">
-        <v>6820619</v>
+        <v>6820448</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3355,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486592</v>
+        <v>121486738</v>
       </c>
       <c r="B28" t="n">
-        <v>74715</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3371,21 +3385,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3395,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499180</v>
+        <v>499060</v>
       </c>
       <c r="R28" t="n">
-        <v>6820509</v>
+        <v>6820435</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3457,10 +3471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486766</v>
+        <v>121486643</v>
       </c>
       <c r="B29" t="n">
-        <v>78345</v>
+        <v>80573</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3473,21 +3487,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3497,10 +3511,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499091</v>
+        <v>499159</v>
       </c>
       <c r="R29" t="n">
-        <v>6820459</v>
+        <v>6820599</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3559,10 +3573,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486703</v>
+        <v>121486626</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>97067</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3571,25 +3585,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499321</v>
+        <v>499104</v>
       </c>
       <c r="R30" t="n">
-        <v>6820523</v>
+        <v>6820567</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486612</v>
+        <v>121486728</v>
       </c>
       <c r="B31" t="n">
-        <v>79719</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,25 +3687,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3701,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499163</v>
+        <v>499103</v>
       </c>
       <c r="R31" t="n">
-        <v>6820511</v>
+        <v>6820567</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3763,10 +3777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486611</v>
+        <v>121486713</v>
       </c>
       <c r="B32" t="n">
-        <v>79719</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,25 +3789,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3803,10 +3817,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499075</v>
+        <v>499123</v>
       </c>
       <c r="R32" t="n">
-        <v>6820457</v>
+        <v>6820323</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3865,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486640</v>
+        <v>121486644</v>
       </c>
       <c r="B33" t="n">
-        <v>79690</v>
+        <v>98113</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,38 +3891,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499110</v>
+        <v>499088</v>
       </c>
       <c r="R33" t="n">
-        <v>6820446</v>
+        <v>6820326</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,6 +3971,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3967,10 +3990,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486646</v>
+        <v>121486721</v>
       </c>
       <c r="B34" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3979,46 +4002,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499124</v>
+        <v>499066</v>
       </c>
       <c r="R34" t="n">
-        <v>6820580</v>
+        <v>6820416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4059,7 +4074,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4078,10 +4092,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486637</v>
+        <v>121486711</v>
       </c>
       <c r="B35" t="n">
-        <v>78346</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4094,21 +4108,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4118,10 +4132,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499221</v>
+        <v>499126</v>
       </c>
       <c r="R35" t="n">
-        <v>6820551</v>
+        <v>6820301</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,10 +4194,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486623</v>
+        <v>121486745</v>
       </c>
       <c r="B36" t="n">
-        <v>79691</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4196,21 +4210,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4220,10 +4234,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499112</v>
+        <v>499219</v>
       </c>
       <c r="R36" t="n">
-        <v>6820448</v>
+        <v>6820563</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4282,10 +4296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486712</v>
+        <v>121486743</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4322,10 +4336,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499123</v>
+        <v>499204</v>
       </c>
       <c r="R37" t="n">
-        <v>6820315</v>
+        <v>6820546</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4384,10 +4398,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486628</v>
+        <v>121486731</v>
       </c>
       <c r="B38" t="n">
-        <v>8435</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4396,47 +4410,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499248</v>
+        <v>499150</v>
       </c>
       <c r="R38" t="n">
-        <v>6820414</v>
+        <v>6820595</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,18 +4476,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4501,10 +4500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486626</v>
+        <v>121486719</v>
       </c>
       <c r="B39" t="n">
-        <v>97059</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4513,25 +4512,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4541,10 +4540,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499104</v>
+        <v>499078</v>
       </c>
       <c r="R39" t="n">
-        <v>6820567</v>
+        <v>6820349</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4603,10 +4602,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486738</v>
+        <v>121486740</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4643,10 +4642,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499060</v>
+        <v>499119</v>
       </c>
       <c r="R40" t="n">
-        <v>6820435</v>
+        <v>6820450</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4705,10 +4704,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486731</v>
+        <v>121486712</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4745,10 +4744,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499150</v>
+        <v>499123</v>
       </c>
       <c r="R41" t="n">
-        <v>6820595</v>
+        <v>6820315</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4807,10 +4806,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486730</v>
+        <v>121486586</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>79234</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4823,21 +4822,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4846,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499159</v>
+        <v>499101</v>
       </c>
       <c r="R42" t="n">
-        <v>6820605</v>
+        <v>6820489</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,10 +4908,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486649</v>
+        <v>121486739</v>
       </c>
       <c r="B43" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4921,46 +4920,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499099</v>
+        <v>499079</v>
       </c>
       <c r="R43" t="n">
-        <v>6820449</v>
+        <v>6820445</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5001,7 +4992,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5020,10 +5010,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486743</v>
+        <v>121486710</v>
       </c>
       <c r="B44" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5060,10 +5050,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499204</v>
+        <v>499134</v>
       </c>
       <c r="R44" t="n">
-        <v>6820546</v>
+        <v>6820297</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5122,10 +5112,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486748</v>
+        <v>121486658</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5138,21 +5128,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5162,10 +5152,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499224</v>
+        <v>499221</v>
       </c>
       <c r="R45" t="n">
-        <v>6820584</v>
+        <v>6820551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5224,10 +5214,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486636</v>
+        <v>121486651</v>
       </c>
       <c r="B46" t="n">
-        <v>78346</v>
+        <v>78352</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5240,21 +5230,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5326,10 +5316,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486729</v>
+        <v>121486591</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>74722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5342,21 +5332,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5366,10 +5356,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499121</v>
+        <v>499060</v>
       </c>
       <c r="R47" t="n">
-        <v>6820578</v>
+        <v>6820434</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5428,10 +5418,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486652</v>
+        <v>121486715</v>
       </c>
       <c r="B48" t="n">
-        <v>78345</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5444,21 +5434,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5458,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499247</v>
+        <v>499085</v>
       </c>
       <c r="R48" t="n">
-        <v>6820414</v>
+        <v>6820324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5520,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486713</v>
+        <v>121486748</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5570,10 +5560,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499123</v>
+        <v>499224</v>
       </c>
       <c r="R49" t="n">
-        <v>6820323</v>
+        <v>6820584</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5632,10 +5622,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486653</v>
+        <v>121486629</v>
       </c>
       <c r="B50" t="n">
-        <v>78345</v>
+        <v>8436</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5644,38 +5634,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499063</v>
+        <v>499088</v>
       </c>
       <c r="R50" t="n">
-        <v>6820418</v>
+        <v>6820469</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5716,6 +5715,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5734,10 +5734,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486728</v>
+        <v>121486766</v>
       </c>
       <c r="B51" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499103</v>
+        <v>499091</v>
       </c>
       <c r="R51" t="n">
-        <v>6820567</v>
+        <v>6820459</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486586</v>
+        <v>121486592</v>
       </c>
       <c r="B52" t="n">
-        <v>79227</v>
+        <v>74722</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499101</v>
+        <v>499180</v>
       </c>
       <c r="R52" t="n">
-        <v>6820489</v>
+        <v>6820509</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
         <v>121475595</v>
       </c>
       <c r="B53" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>121475875</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486649</v>
+        <v>121486654</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>78352</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,46 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499099</v>
+        <v>499174</v>
       </c>
       <c r="R7" t="n">
-        <v>6820449</v>
+        <v>6820509</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486654</v>
+        <v>121486703</v>
       </c>
       <c r="B8" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499174</v>
+        <v>499321</v>
       </c>
       <c r="R8" t="n">
-        <v>6820509</v>
+        <v>6820523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486703</v>
+        <v>121486649</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,38 +1401,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499321</v>
+        <v>499099</v>
       </c>
       <c r="R9" t="n">
-        <v>6820523</v>
+        <v>6820449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,6 +1481,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486744</v>
+        <v>121486729</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499210</v>
+        <v>499121</v>
       </c>
       <c r="R17" t="n">
-        <v>6820548</v>
+        <v>6820578</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486729</v>
+        <v>121486717</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499121</v>
+        <v>499081</v>
       </c>
       <c r="R18" t="n">
-        <v>6820578</v>
+        <v>6820327</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486717</v>
+        <v>121486653</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499081</v>
+        <v>499063</v>
       </c>
       <c r="R19" t="n">
-        <v>6820327</v>
+        <v>6820418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486653</v>
+        <v>121486611</v>
       </c>
       <c r="B20" t="n">
-        <v>78352</v>
+        <v>79726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499063</v>
+        <v>499075</v>
       </c>
       <c r="R20" t="n">
-        <v>6820418</v>
+        <v>6820457</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486611</v>
+        <v>121486744</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499075</v>
+        <v>499210</v>
       </c>
       <c r="R21" t="n">
-        <v>6820457</v>
+        <v>6820548</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486646</v>
+        <v>121486623</v>
       </c>
       <c r="B25" t="n">
-        <v>98113</v>
+        <v>79698</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3066,46 +3066,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499124</v>
+        <v>499112</v>
       </c>
       <c r="R25" t="n">
-        <v>6820580</v>
+        <v>6820448</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,7 +3138,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3165,10 +3156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486637</v>
+        <v>121486646</v>
       </c>
       <c r="B26" t="n">
-        <v>78353</v>
+        <v>98113</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3177,38 +3168,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499221</v>
+        <v>499124</v>
       </c>
       <c r="R26" t="n">
-        <v>6820551</v>
+        <v>6820580</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,6 +3248,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486623</v>
+        <v>121486637</v>
       </c>
       <c r="B27" t="n">
-        <v>79698</v>
+        <v>78353</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499112</v>
+        <v>499221</v>
       </c>
       <c r="R27" t="n">
-        <v>6820448</v>
+        <v>6820551</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486711</v>
+        <v>121486745</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499126</v>
+        <v>499219</v>
       </c>
       <c r="R35" t="n">
-        <v>6820301</v>
+        <v>6820563</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486745</v>
+        <v>121486711</v>
       </c>
       <c r="B36" t="n">
         <v>78616</v>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499219</v>
+        <v>499126</v>
       </c>
       <c r="R36" t="n">
-        <v>6820563</v>
+        <v>6820301</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486654</v>
+        <v>121486649</v>
       </c>
       <c r="B7" t="n">
-        <v>78352</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499174</v>
+        <v>499099</v>
       </c>
       <c r="R7" t="n">
-        <v>6820509</v>
+        <v>6820449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1277,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486703</v>
+        <v>121486654</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499321</v>
+        <v>499174</v>
       </c>
       <c r="R8" t="n">
-        <v>6820523</v>
+        <v>6820509</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486649</v>
+        <v>121486703</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,46 +1410,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499099</v>
+        <v>499321</v>
       </c>
       <c r="R9" t="n">
-        <v>6820449</v>
+        <v>6820523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,7 +1482,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486745</v>
+        <v>121486711</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499219</v>
+        <v>499126</v>
       </c>
       <c r="R35" t="n">
-        <v>6820563</v>
+        <v>6820301</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486711</v>
+        <v>121486745</v>
       </c>
       <c r="B36" t="n">
         <v>78616</v>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499126</v>
+        <v>499219</v>
       </c>
       <c r="R36" t="n">
-        <v>6820301</v>
+        <v>6820563</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486738</v>
+        <v>121486729</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499060</v>
+        <v>499121</v>
       </c>
       <c r="R2" t="n">
-        <v>6820435</v>
+        <v>6820578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486730</v>
+        <v>121486715</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499159</v>
+        <v>499085</v>
       </c>
       <c r="R3" t="n">
-        <v>6820605</v>
+        <v>6820324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486586</v>
+        <v>121486739</v>
       </c>
       <c r="B4" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499101</v>
+        <v>499079</v>
       </c>
       <c r="R4" t="n">
-        <v>6820489</v>
+        <v>6820445</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486641</v>
+        <v>121486592</v>
       </c>
       <c r="B5" t="n">
-        <v>79697</v>
+        <v>74722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499241</v>
+        <v>499180</v>
       </c>
       <c r="R5" t="n">
-        <v>6820619</v>
+        <v>6820509</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486745</v>
+        <v>121486654</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499219</v>
+        <v>499174</v>
       </c>
       <c r="R6" t="n">
-        <v>6820563</v>
+        <v>6820509</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486653</v>
+        <v>121486712</v>
       </c>
       <c r="B7" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499063</v>
+        <v>499123</v>
       </c>
       <c r="R7" t="n">
-        <v>6820418</v>
+        <v>6820315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486591</v>
+        <v>121486643</v>
       </c>
       <c r="B8" t="n">
-        <v>74722</v>
+        <v>80573</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499060</v>
+        <v>499159</v>
       </c>
       <c r="R8" t="n">
-        <v>6820434</v>
+        <v>6820599</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486635</v>
+        <v>121486626</v>
       </c>
       <c r="B9" t="n">
-        <v>78353</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499279</v>
+        <v>499104</v>
       </c>
       <c r="R9" t="n">
-        <v>6820470</v>
+        <v>6820567</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486587</v>
+        <v>121486766</v>
       </c>
       <c r="B10" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499137</v>
+        <v>499091</v>
       </c>
       <c r="R10" t="n">
-        <v>6820469</v>
+        <v>6820459</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486743</v>
+        <v>121486587</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499204</v>
+        <v>499137</v>
       </c>
       <c r="R11" t="n">
-        <v>6820546</v>
+        <v>6820469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486748</v>
+        <v>121486640</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499224</v>
+        <v>499110</v>
       </c>
       <c r="R12" t="n">
-        <v>6820584</v>
+        <v>6820446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486720</v>
+        <v>121486644</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499064</v>
+        <v>499088</v>
       </c>
       <c r="R13" t="n">
-        <v>6820411</v>
+        <v>6820326</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1881,6 +1889,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1899,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486640</v>
+        <v>121486722</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499110</v>
+        <v>499063</v>
       </c>
       <c r="R14" t="n">
-        <v>6820446</v>
+        <v>6820429</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2010,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486658</v>
+        <v>121486653</v>
       </c>
       <c r="B15" t="n">
         <v>78352</v>
@@ -2041,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499221</v>
+        <v>499063</v>
       </c>
       <c r="R15" t="n">
-        <v>6820551</v>
+        <v>6820418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486703</v>
+        <v>121486651</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499321</v>
+        <v>499244</v>
       </c>
       <c r="R16" t="n">
-        <v>6820523</v>
+        <v>6820418</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486718</v>
+        <v>121486646</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,38 +2226,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499079</v>
+        <v>499124</v>
       </c>
       <c r="R17" t="n">
-        <v>6820344</v>
+        <v>6820580</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2289,6 +2306,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2307,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486744</v>
+        <v>121486648</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,38 +2337,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499210</v>
+        <v>499087</v>
       </c>
       <c r="R18" t="n">
-        <v>6820548</v>
+        <v>6820462</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,6 +2417,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2409,10 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486626</v>
+        <v>121486623</v>
       </c>
       <c r="B19" t="n">
-        <v>97067</v>
+        <v>79698</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2448,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499104</v>
+        <v>499112</v>
       </c>
       <c r="R19" t="n">
-        <v>6820567</v>
+        <v>6820448</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2538,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486643</v>
+        <v>121486591</v>
       </c>
       <c r="B20" t="n">
-        <v>80573</v>
+        <v>74722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2554,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2578,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499159</v>
+        <v>499060</v>
       </c>
       <c r="R20" t="n">
-        <v>6820599</v>
+        <v>6820434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2640,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486713</v>
+        <v>121486720</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2653,10 +2680,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499123</v>
+        <v>499064</v>
       </c>
       <c r="R21" t="n">
-        <v>6820323</v>
+        <v>6820411</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2742,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486628</v>
+        <v>121486714</v>
       </c>
       <c r="B22" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,47 +2754,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499248</v>
+        <v>499120</v>
       </c>
       <c r="R22" t="n">
-        <v>6820414</v>
+        <v>6820327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2802,18 +2820,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2832,10 +2844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486629</v>
+        <v>121486636</v>
       </c>
       <c r="B23" t="n">
-        <v>8436</v>
+        <v>78353</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2844,47 +2856,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499088</v>
+        <v>499244</v>
       </c>
       <c r="R23" t="n">
-        <v>6820469</v>
+        <v>6820418</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,7 +2928,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2944,10 +2946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486592</v>
+        <v>121486742</v>
       </c>
       <c r="B24" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,21 +2962,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2986,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499180</v>
+        <v>499140</v>
       </c>
       <c r="R24" t="n">
-        <v>6820509</v>
+        <v>6820485</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,7 +3048,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486739</v>
+        <v>121486717</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3086,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499079</v>
+        <v>499081</v>
       </c>
       <c r="R25" t="n">
-        <v>6820445</v>
+        <v>6820327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3150,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486731</v>
+        <v>121486649</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,38 +3162,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499150</v>
+        <v>499099</v>
       </c>
       <c r="R26" t="n">
-        <v>6820595</v>
+        <v>6820449</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3232,6 +3242,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3250,7 +3261,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486719</v>
+        <v>121486745</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3290,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499078</v>
+        <v>499219</v>
       </c>
       <c r="R27" t="n">
-        <v>6820349</v>
+        <v>6820563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,7 +3363,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486728</v>
+        <v>121486740</v>
       </c>
       <c r="B28" t="n">
         <v>78616</v>
@@ -3392,10 +3403,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499103</v>
+        <v>499119</v>
       </c>
       <c r="R28" t="n">
-        <v>6820567</v>
+        <v>6820450</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,7 +3465,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486714</v>
+        <v>121486703</v>
       </c>
       <c r="B29" t="n">
         <v>78616</v>
@@ -3494,10 +3505,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499120</v>
+        <v>499321</v>
       </c>
       <c r="R29" t="n">
-        <v>6820327</v>
+        <v>6820523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3567,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486636</v>
+        <v>121486719</v>
       </c>
       <c r="B30" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,21 +3583,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3607,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499244</v>
+        <v>499078</v>
       </c>
       <c r="R30" t="n">
-        <v>6820418</v>
+        <v>6820349</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,10 +3669,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486652</v>
+        <v>121486628</v>
       </c>
       <c r="B31" t="n">
-        <v>78352</v>
+        <v>8436</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,35 +3681,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499247</v>
+        <v>499248</v>
       </c>
       <c r="R31" t="n">
         <v>6820414</v>
@@ -3736,12 +3756,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3760,10 +3786,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486612</v>
+        <v>121486637</v>
       </c>
       <c r="B32" t="n">
-        <v>79726</v>
+        <v>78353</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,25 +3798,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499163</v>
+        <v>499221</v>
       </c>
       <c r="R32" t="n">
-        <v>6820511</v>
+        <v>6820551</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,7 +3888,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486711</v>
+        <v>121486731</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -3902,10 +3928,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499126</v>
+        <v>499150</v>
       </c>
       <c r="R33" t="n">
-        <v>6820301</v>
+        <v>6820595</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,7 +3990,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486712</v>
+        <v>121486744</v>
       </c>
       <c r="B34" t="n">
         <v>78616</v>
@@ -4004,10 +4030,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499123</v>
+        <v>499210</v>
       </c>
       <c r="R34" t="n">
-        <v>6820315</v>
+        <v>6820548</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4092,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486742</v>
+        <v>121486641</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,21 +4108,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +4132,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499140</v>
+        <v>499241</v>
       </c>
       <c r="R35" t="n">
-        <v>6820485</v>
+        <v>6820619</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4194,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486654</v>
+        <v>121486635</v>
       </c>
       <c r="B36" t="n">
-        <v>78352</v>
+        <v>78353</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,21 +4210,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4234,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499174</v>
+        <v>499279</v>
       </c>
       <c r="R36" t="n">
-        <v>6820509</v>
+        <v>6820470</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4296,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486729</v>
+        <v>121486718</v>
       </c>
       <c r="B37" t="n">
         <v>78616</v>
@@ -4310,10 +4336,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499121</v>
+        <v>499079</v>
       </c>
       <c r="R37" t="n">
-        <v>6820578</v>
+        <v>6820344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4398,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486623</v>
+        <v>121486612</v>
       </c>
       <c r="B38" t="n">
-        <v>79698</v>
+        <v>79726</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4410,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4438,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499112</v>
+        <v>499163</v>
       </c>
       <c r="R38" t="n">
-        <v>6820448</v>
+        <v>6820511</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486644</v>
+        <v>121486629</v>
       </c>
       <c r="B39" t="n">
-        <v>98113</v>
+        <v>8436</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4486,35 +4512,36 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4525,7 +4552,7 @@
         <v>499088</v>
       </c>
       <c r="R39" t="n">
-        <v>6820326</v>
+        <v>6820469</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4585,10 +4612,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486766</v>
+        <v>121486711</v>
       </c>
       <c r="B40" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4601,21 +4628,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4625,10 +4652,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499091</v>
+        <v>499126</v>
       </c>
       <c r="R40" t="n">
-        <v>6820459</v>
+        <v>6820301</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4687,7 +4714,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486710</v>
+        <v>121486728</v>
       </c>
       <c r="B41" t="n">
         <v>78616</v>
@@ -4727,10 +4754,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499134</v>
+        <v>499103</v>
       </c>
       <c r="R41" t="n">
-        <v>6820297</v>
+        <v>6820567</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4789,10 +4816,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486646</v>
+        <v>121486658</v>
       </c>
       <c r="B42" t="n">
-        <v>98113</v>
+        <v>78352</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,46 +4828,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499124</v>
+        <v>499221</v>
       </c>
       <c r="R42" t="n">
-        <v>6820580</v>
+        <v>6820551</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,7 +4900,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4900,10 +4918,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486648</v>
+        <v>121486730</v>
       </c>
       <c r="B43" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4912,46 +4930,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499087</v>
+        <v>499159</v>
       </c>
       <c r="R43" t="n">
-        <v>6820462</v>
+        <v>6820605</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,7 +5002,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5011,10 +5020,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486649</v>
+        <v>121486611</v>
       </c>
       <c r="B44" t="n">
-        <v>98113</v>
+        <v>79726</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5023,46 +5032,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499099</v>
+        <v>499075</v>
       </c>
       <c r="R44" t="n">
-        <v>6820449</v>
+        <v>6820457</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,7 +5104,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5122,10 +5122,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486651</v>
+        <v>121486713</v>
       </c>
       <c r="B45" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499244</v>
+        <v>499123</v>
       </c>
       <c r="R45" t="n">
-        <v>6820418</v>
+        <v>6820323</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486637</v>
+        <v>121486748</v>
       </c>
       <c r="B46" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499221</v>
+        <v>499224</v>
       </c>
       <c r="R46" t="n">
-        <v>6820551</v>
+        <v>6820584</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486740</v>
+        <v>121486743</v>
       </c>
       <c r="B47" t="n">
         <v>78616</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499119</v>
+        <v>499204</v>
       </c>
       <c r="R47" t="n">
-        <v>6820450</v>
+        <v>6820546</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5428,10 +5428,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486715</v>
+        <v>121486652</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499085</v>
+        <v>499247</v>
       </c>
       <c r="R48" t="n">
-        <v>6820324</v>
+        <v>6820414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486717</v>
+        <v>121486586</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499081</v>
+        <v>499101</v>
       </c>
       <c r="R49" t="n">
-        <v>6820327</v>
+        <v>6820489</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486611</v>
+        <v>121486738</v>
       </c>
       <c r="B50" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5644,25 +5644,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499075</v>
+        <v>499060</v>
       </c>
       <c r="R50" t="n">
-        <v>6820457</v>
+        <v>6820435</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5734,7 +5734,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486722</v>
+        <v>121486710</v>
       </c>
       <c r="B51" t="n">
         <v>78616</v>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499063</v>
+        <v>499134</v>
       </c>
       <c r="R51" t="n">
-        <v>6820429</v>
+        <v>6820297</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486766</v>
+        <v>121486640</v>
       </c>
       <c r="B10" t="n">
-        <v>78352</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499091</v>
+        <v>499110</v>
       </c>
       <c r="R10" t="n">
-        <v>6820459</v>
+        <v>6820446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486587</v>
+        <v>121486766</v>
       </c>
       <c r="B11" t="n">
-        <v>79234</v>
+        <v>78352</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499137</v>
+        <v>499091</v>
       </c>
       <c r="R11" t="n">
-        <v>6820469</v>
+        <v>6820459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486640</v>
+        <v>121486587</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
+        <v>79234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499110</v>
+        <v>499137</v>
       </c>
       <c r="R12" t="n">
-        <v>6820446</v>
+        <v>6820469</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486612</v>
+        <v>121486629</v>
       </c>
       <c r="B38" t="n">
-        <v>79726</v>
+        <v>8436</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4414,34 +4414,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499163</v>
+        <v>499088</v>
       </c>
       <c r="R38" t="n">
-        <v>6820511</v>
+        <v>6820469</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4482,6 +4491,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4500,10 +4510,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486629</v>
+        <v>121486612</v>
       </c>
       <c r="B39" t="n">
-        <v>8436</v>
+        <v>79726</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4516,43 +4526,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499088</v>
+        <v>499163</v>
       </c>
       <c r="R39" t="n">
-        <v>6820469</v>
+        <v>6820511</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4593,7 +4594,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5122,7 +5122,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486713</v>
+        <v>121486748</v>
       </c>
       <c r="B45" t="n">
         <v>78616</v>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499123</v>
+        <v>499224</v>
       </c>
       <c r="R45" t="n">
-        <v>6820323</v>
+        <v>6820584</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486748</v>
+        <v>121486713</v>
       </c>
       <c r="B46" t="n">
         <v>78616</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499224</v>
+        <v>499123</v>
       </c>
       <c r="R46" t="n">
-        <v>6820584</v>
+        <v>6820323</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486729</v>
+        <v>121486644</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499121</v>
+        <v>499088</v>
       </c>
       <c r="R2" t="n">
-        <v>6820578</v>
+        <v>6820326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486715</v>
+        <v>121486743</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499085</v>
+        <v>499204</v>
       </c>
       <c r="R3" t="n">
-        <v>6820324</v>
+        <v>6820546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486592</v>
+        <v>121486721</v>
       </c>
       <c r="B5" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499180</v>
+        <v>499066</v>
       </c>
       <c r="R5" t="n">
-        <v>6820509</v>
+        <v>6820416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486712</v>
+        <v>121486640</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499123</v>
+        <v>499110</v>
       </c>
       <c r="R7" t="n">
-        <v>6820315</v>
+        <v>6820446</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486643</v>
+        <v>121486611</v>
       </c>
       <c r="B8" t="n">
-        <v>80573</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499159</v>
+        <v>499075</v>
       </c>
       <c r="R8" t="n">
-        <v>6820599</v>
+        <v>6820457</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486626</v>
+        <v>121486719</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499104</v>
+        <v>499078</v>
       </c>
       <c r="R9" t="n">
-        <v>6820567</v>
+        <v>6820349</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486640</v>
+        <v>121486591</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>74722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499110</v>
+        <v>499060</v>
       </c>
       <c r="R10" t="n">
-        <v>6820446</v>
+        <v>6820434</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486766</v>
+        <v>121486744</v>
       </c>
       <c r="B11" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499091</v>
+        <v>499210</v>
       </c>
       <c r="R11" t="n">
-        <v>6820459</v>
+        <v>6820548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486587</v>
+        <v>121486730</v>
       </c>
       <c r="B12" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499137</v>
+        <v>499159</v>
       </c>
       <c r="R12" t="n">
-        <v>6820469</v>
+        <v>6820605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486644</v>
+        <v>121486722</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,46 +1818,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499088</v>
+        <v>499063</v>
       </c>
       <c r="R13" t="n">
-        <v>6820326</v>
+        <v>6820429</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,7 +1890,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486722</v>
+        <v>121486728</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499063</v>
+        <v>499103</v>
       </c>
       <c r="R14" t="n">
-        <v>6820429</v>
+        <v>6820567</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486653</v>
+        <v>121486635</v>
       </c>
       <c r="B15" t="n">
-        <v>78352</v>
+        <v>78353</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499063</v>
+        <v>499279</v>
       </c>
       <c r="R15" t="n">
-        <v>6820418</v>
+        <v>6820470</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486651</v>
+        <v>121486731</v>
       </c>
       <c r="B16" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499244</v>
+        <v>499150</v>
       </c>
       <c r="R16" t="n">
-        <v>6820418</v>
+        <v>6820595</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486646</v>
+        <v>121486658</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>78352</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,46 +2226,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499124</v>
+        <v>499221</v>
       </c>
       <c r="R17" t="n">
-        <v>6820580</v>
+        <v>6820551</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,7 +2298,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2325,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486648</v>
+        <v>121486717</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,46 +2328,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499087</v>
+        <v>499081</v>
       </c>
       <c r="R18" t="n">
-        <v>6820462</v>
+        <v>6820327</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,7 +2400,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2436,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486623</v>
+        <v>121486729</v>
       </c>
       <c r="B19" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2452,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499112</v>
+        <v>499121</v>
       </c>
       <c r="R19" t="n">
-        <v>6820448</v>
+        <v>6820578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486591</v>
+        <v>121486652</v>
       </c>
       <c r="B20" t="n">
-        <v>74722</v>
+        <v>78352</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2554,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2578,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499060</v>
+        <v>499247</v>
       </c>
       <c r="R20" t="n">
-        <v>6820434</v>
+        <v>6820414</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,7 +2622,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486720</v>
+        <v>121486745</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2680,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499064</v>
+        <v>499219</v>
       </c>
       <c r="R21" t="n">
-        <v>6820411</v>
+        <v>6820563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,7 +2724,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486714</v>
+        <v>121486703</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -2782,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499120</v>
+        <v>499321</v>
       </c>
       <c r="R22" t="n">
-        <v>6820327</v>
+        <v>6820523</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2844,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486636</v>
+        <v>121486641</v>
       </c>
       <c r="B23" t="n">
-        <v>78353</v>
+        <v>79697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2860,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2884,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499244</v>
+        <v>499241</v>
       </c>
       <c r="R23" t="n">
-        <v>6820418</v>
+        <v>6820619</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486717</v>
+        <v>121486592</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3064,21 +3046,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3088,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499081</v>
+        <v>499180</v>
       </c>
       <c r="R25" t="n">
-        <v>6820327</v>
+        <v>6820509</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486649</v>
+        <v>121486629</v>
       </c>
       <c r="B26" t="n">
-        <v>98113</v>
+        <v>8436</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3162,35 +3144,36 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3198,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499099</v>
+        <v>499088</v>
       </c>
       <c r="R26" t="n">
-        <v>6820449</v>
+        <v>6820469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,10 +3244,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486745</v>
+        <v>121486766</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3277,21 +3260,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3301,10 +3284,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499219</v>
+        <v>499091</v>
       </c>
       <c r="R27" t="n">
-        <v>6820563</v>
+        <v>6820459</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3363,7 +3346,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486740</v>
+        <v>121486715</v>
       </c>
       <c r="B28" t="n">
         <v>78616</v>
@@ -3403,10 +3386,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499119</v>
+        <v>499085</v>
       </c>
       <c r="R28" t="n">
-        <v>6820450</v>
+        <v>6820324</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3465,7 +3448,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486703</v>
+        <v>121486714</v>
       </c>
       <c r="B29" t="n">
         <v>78616</v>
@@ -3505,10 +3488,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499321</v>
+        <v>499120</v>
       </c>
       <c r="R29" t="n">
-        <v>6820523</v>
+        <v>6820327</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3567,10 +3550,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486719</v>
+        <v>121486626</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3579,25 +3562,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3607,10 +3590,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499078</v>
+        <v>499104</v>
       </c>
       <c r="R30" t="n">
-        <v>6820349</v>
+        <v>6820567</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486628</v>
+        <v>121486636</v>
       </c>
       <c r="B31" t="n">
-        <v>8436</v>
+        <v>78353</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3681,47 +3664,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499248</v>
+        <v>499244</v>
       </c>
       <c r="R31" t="n">
-        <v>6820414</v>
+        <v>6820418</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3756,18 +3730,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3786,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486637</v>
+        <v>121486711</v>
       </c>
       <c r="B32" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3802,21 +3770,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499221</v>
+        <v>499126</v>
       </c>
       <c r="R32" t="n">
-        <v>6820551</v>
+        <v>6820301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3888,7 +3856,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486731</v>
+        <v>121486712</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -3928,10 +3896,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499150</v>
+        <v>499123</v>
       </c>
       <c r="R33" t="n">
-        <v>6820595</v>
+        <v>6820315</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3990,10 +3958,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486744</v>
+        <v>121486612</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4002,25 +3970,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4030,10 +3998,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499210</v>
+        <v>499163</v>
       </c>
       <c r="R34" t="n">
-        <v>6820548</v>
+        <v>6820511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4092,10 +4060,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486641</v>
+        <v>121486643</v>
       </c>
       <c r="B35" t="n">
-        <v>79697</v>
+        <v>80573</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4108,21 +4076,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4132,10 +4100,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499241</v>
+        <v>499159</v>
       </c>
       <c r="R35" t="n">
-        <v>6820619</v>
+        <v>6820599</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,10 +4162,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486635</v>
+        <v>121486648</v>
       </c>
       <c r="B36" t="n">
-        <v>78353</v>
+        <v>98113</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4206,38 +4174,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>499279</v>
+        <v>499087</v>
       </c>
       <c r="R36" t="n">
-        <v>6820470</v>
+        <v>6820462</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4278,6 +4254,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4296,10 +4273,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486718</v>
+        <v>121486651</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4312,21 +4289,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4336,10 +4313,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499079</v>
+        <v>499244</v>
       </c>
       <c r="R37" t="n">
-        <v>6820344</v>
+        <v>6820418</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4398,10 +4375,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486629</v>
+        <v>121486738</v>
       </c>
       <c r="B38" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4410,47 +4387,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499088</v>
+        <v>499060</v>
       </c>
       <c r="R38" t="n">
-        <v>6820469</v>
+        <v>6820435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4491,7 +4459,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4510,10 +4477,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486612</v>
+        <v>121486628</v>
       </c>
       <c r="B39" t="n">
-        <v>79726</v>
+        <v>8436</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4526,34 +4493,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499163</v>
+        <v>499248</v>
       </c>
       <c r="R39" t="n">
-        <v>6820511</v>
+        <v>6820414</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4588,12 +4564,18 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4612,7 +4594,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486711</v>
+        <v>121486720</v>
       </c>
       <c r="B40" t="n">
         <v>78616</v>
@@ -4652,10 +4634,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499126</v>
+        <v>499064</v>
       </c>
       <c r="R40" t="n">
-        <v>6820301</v>
+        <v>6820411</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,7 +4696,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486728</v>
+        <v>121486710</v>
       </c>
       <c r="B41" t="n">
         <v>78616</v>
@@ -4754,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499103</v>
+        <v>499134</v>
       </c>
       <c r="R41" t="n">
-        <v>6820567</v>
+        <v>6820297</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4816,10 +4798,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486658</v>
+        <v>121486748</v>
       </c>
       <c r="B42" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4832,21 +4814,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4856,10 +4838,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499221</v>
+        <v>499224</v>
       </c>
       <c r="R42" t="n">
-        <v>6820551</v>
+        <v>6820584</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4918,10 +4900,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486730</v>
+        <v>121486649</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4930,38 +4912,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499159</v>
+        <v>499099</v>
       </c>
       <c r="R43" t="n">
-        <v>6820605</v>
+        <v>6820449</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5002,6 +4992,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5020,10 +5011,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486611</v>
+        <v>121486740</v>
       </c>
       <c r="B44" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5032,25 +5023,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5060,10 +5051,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499075</v>
+        <v>499119</v>
       </c>
       <c r="R44" t="n">
-        <v>6820457</v>
+        <v>6820450</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5122,10 +5113,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486748</v>
+        <v>121486623</v>
       </c>
       <c r="B45" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5138,21 +5129,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5162,10 +5153,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499224</v>
+        <v>499112</v>
       </c>
       <c r="R45" t="n">
-        <v>6820584</v>
+        <v>6820448</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5224,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486713</v>
+        <v>121486586</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5240,21 +5231,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5264,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499123</v>
+        <v>499101</v>
       </c>
       <c r="R46" t="n">
-        <v>6820323</v>
+        <v>6820489</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5326,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486743</v>
+        <v>121486587</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5342,21 +5333,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5366,10 +5357,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499204</v>
+        <v>499137</v>
       </c>
       <c r="R47" t="n">
-        <v>6820546</v>
+        <v>6820469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5428,10 +5419,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486652</v>
+        <v>121486718</v>
       </c>
       <c r="B48" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5444,21 +5435,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5468,10 +5459,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499247</v>
+        <v>499079</v>
       </c>
       <c r="R48" t="n">
-        <v>6820414</v>
+        <v>6820344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5530,10 +5521,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486586</v>
+        <v>121486637</v>
       </c>
       <c r="B49" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5546,21 +5537,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5561,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499101</v>
+        <v>499221</v>
       </c>
       <c r="R49" t="n">
-        <v>6820489</v>
+        <v>6820551</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5632,10 +5623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486738</v>
+        <v>121486653</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,21 +5639,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5672,10 +5663,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499060</v>
+        <v>499063</v>
       </c>
       <c r="R50" t="n">
-        <v>6820435</v>
+        <v>6820418</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5734,7 +5725,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486710</v>
+        <v>121486713</v>
       </c>
       <c r="B51" t="n">
         <v>78616</v>
@@ -5774,10 +5765,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499134</v>
+        <v>499123</v>
       </c>
       <c r="R51" t="n">
-        <v>6820297</v>
+        <v>6820323</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,10 +5827,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486721</v>
+        <v>121486646</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5848,38 +5839,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499066</v>
+        <v>499124</v>
       </c>
       <c r="R52" t="n">
-        <v>6820416</v>
+        <v>6820580</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5920,6 +5919,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121486644</v>
+        <v>121486643</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499088</v>
+        <v>499159</v>
       </c>
       <c r="R2" t="n">
-        <v>6820326</v>
+        <v>6820599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121486743</v>
+        <v>121486622</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499204</v>
+        <v>499291</v>
       </c>
       <c r="R3" t="n">
-        <v>6820546</v>
+        <v>6820602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121486739</v>
+        <v>121486623</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499079</v>
+        <v>499112</v>
       </c>
       <c r="R4" t="n">
-        <v>6820445</v>
+        <v>6820448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121486721</v>
+        <v>121488299</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,37 +977,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499066</v>
+        <v>499261</v>
       </c>
       <c r="R5" t="n">
-        <v>6820416</v>
+        <v>6820633</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,33 +1048,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121486654</v>
+        <v>121488306</v>
       </c>
       <c r="B6" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,37 +1078,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499174</v>
+        <v>499283</v>
       </c>
       <c r="R6" t="n">
-        <v>6820509</v>
+        <v>6820577</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,71 +1149,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121486640</v>
+        <v>121475875</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Dlr</t>
+          <t>Långtallarna, Långtallarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499110</v>
+        <v>499095</v>
       </c>
       <c r="R7" t="n">
-        <v>6820446</v>
+        <v>6820473</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,9 +1236,19 @@
           <t>2024-12-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,49 +1263,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121486611</v>
+        <v>121486700</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499075</v>
+        <v>499335</v>
       </c>
       <c r="R8" t="n">
-        <v>6820457</v>
+        <v>6820629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,19 +1372,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121486719</v>
+        <v>121486701</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1438,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499078</v>
+        <v>499325</v>
       </c>
       <c r="R9" t="n">
-        <v>6820349</v>
+        <v>6820620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,37 +1469,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121486591</v>
+        <v>121486702</v>
       </c>
       <c r="B10" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499060</v>
+        <v>499302</v>
       </c>
       <c r="R10" t="n">
-        <v>6820434</v>
+        <v>6820599</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,19 +1566,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121486744</v>
+        <v>121486703</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1642,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499210</v>
+        <v>499321</v>
       </c>
       <c r="R11" t="n">
-        <v>6820548</v>
+        <v>6820523</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,19 +1663,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121486730</v>
+        <v>121486705</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1744,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499159</v>
+        <v>499242</v>
       </c>
       <c r="R12" t="n">
-        <v>6820605</v>
+        <v>6820395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,19 +1760,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121486722</v>
+        <v>121486706</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1846,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499063</v>
+        <v>499218</v>
       </c>
       <c r="R13" t="n">
-        <v>6820429</v>
+        <v>6820363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,19 +1857,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121486728</v>
+        <v>121486707</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1948,10 +1892,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499103</v>
+        <v>499216</v>
       </c>
       <c r="R14" t="n">
-        <v>6820567</v>
+        <v>6820349</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,37 +1954,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121486635</v>
+        <v>121486708</v>
       </c>
       <c r="B15" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +1989,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499279</v>
+        <v>499203</v>
       </c>
       <c r="R15" t="n">
-        <v>6820470</v>
+        <v>6820342</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,19 +2051,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121486731</v>
+        <v>121486709</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2152,10 +2086,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499150</v>
+        <v>499193</v>
       </c>
       <c r="R16" t="n">
-        <v>6820595</v>
+        <v>6820310</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,37 +2148,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121486658</v>
+        <v>121486710</v>
       </c>
       <c r="B17" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2183,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499221</v>
+        <v>499134</v>
       </c>
       <c r="R17" t="n">
-        <v>6820551</v>
+        <v>6820297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,19 +2245,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121486729</v>
+        <v>121486711</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2356,10 +2280,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499121</v>
+        <v>499126</v>
       </c>
       <c r="R18" t="n">
-        <v>6820578</v>
+        <v>6820301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,37 +2342,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121486652</v>
+        <v>121486712</v>
       </c>
       <c r="B19" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499247</v>
+        <v>499123</v>
       </c>
       <c r="R19" t="n">
-        <v>6820414</v>
+        <v>6820315</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,19 +2439,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121486745</v>
+        <v>121486713</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2560,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499219</v>
+        <v>499123</v>
       </c>
       <c r="R20" t="n">
-        <v>6820563</v>
+        <v>6820323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,19 +2536,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121486703</v>
+        <v>121486714</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2662,10 +2571,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499321</v>
+        <v>499120</v>
       </c>
       <c r="R21" t="n">
-        <v>6820523</v>
+        <v>6820327</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,19 +2633,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121486717</v>
+        <v>121486715</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2764,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499081</v>
+        <v>499085</v>
       </c>
       <c r="R22" t="n">
-        <v>6820327</v>
+        <v>6820324</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,37 +2730,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121486641</v>
+        <v>121486717</v>
       </c>
       <c r="B23" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2765,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499241</v>
+        <v>499081</v>
       </c>
       <c r="R23" t="n">
-        <v>6820619</v>
+        <v>6820327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,19 +2827,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121486742</v>
+        <v>121486718</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2968,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499140</v>
+        <v>499079</v>
       </c>
       <c r="R24" t="n">
-        <v>6820485</v>
+        <v>6820344</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,37 +2924,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121486592</v>
+        <v>121486719</v>
       </c>
       <c r="B25" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +2959,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499180</v>
+        <v>499078</v>
       </c>
       <c r="R25" t="n">
-        <v>6820509</v>
+        <v>6820349</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,59 +3021,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121486629</v>
+        <v>121486720</v>
       </c>
       <c r="B26" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499088</v>
+        <v>499064</v>
       </c>
       <c r="R26" t="n">
-        <v>6820469</v>
+        <v>6820411</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3100,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3244,37 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121486766</v>
+        <v>121486721</v>
       </c>
       <c r="B27" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3284,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499091</v>
+        <v>499066</v>
       </c>
       <c r="R27" t="n">
-        <v>6820459</v>
+        <v>6820416</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,19 +3215,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121486715</v>
+        <v>121486722</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3386,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499085</v>
+        <v>499063</v>
       </c>
       <c r="R28" t="n">
-        <v>6820324</v>
+        <v>6820429</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,19 +3312,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121486714</v>
+        <v>121486723</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3488,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499120</v>
+        <v>499066</v>
       </c>
       <c r="R29" t="n">
-        <v>6820327</v>
+        <v>6820518</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3550,37 +3409,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121486626</v>
+        <v>121486724</v>
       </c>
       <c r="B30" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3590,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499104</v>
+        <v>499059</v>
       </c>
       <c r="R30" t="n">
-        <v>6820567</v>
+        <v>6820515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,37 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121486636</v>
+        <v>121486725</v>
       </c>
       <c r="B31" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3692,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499244</v>
+        <v>499046</v>
       </c>
       <c r="R31" t="n">
-        <v>6820418</v>
+        <v>6820535</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,19 +3603,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121486711</v>
+        <v>121486726</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3794,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499126</v>
+        <v>499070</v>
       </c>
       <c r="R32" t="n">
-        <v>6820301</v>
+        <v>6820544</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3856,19 +3700,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121486712</v>
+        <v>121486727</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3896,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>499123</v>
+        <v>499085</v>
       </c>
       <c r="R33" t="n">
-        <v>6820315</v>
+        <v>6820555</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3958,37 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121486612</v>
+        <v>121486728</v>
       </c>
       <c r="B34" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3998,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499163</v>
+        <v>499103</v>
       </c>
       <c r="R34" t="n">
-        <v>6820511</v>
+        <v>6820567</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4060,37 +3894,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121486651</v>
+        <v>121486729</v>
       </c>
       <c r="B35" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4100,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>499244</v>
+        <v>499121</v>
       </c>
       <c r="R35" t="n">
-        <v>6820418</v>
+        <v>6820578</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,37 +3991,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121486643</v>
+        <v>121486730</v>
       </c>
       <c r="B36" t="n">
-        <v>80573</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4205,7 +4029,7 @@
         <v>499159</v>
       </c>
       <c r="R36" t="n">
-        <v>6820599</v>
+        <v>6820605</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,15 +4088,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121486648</v>
+        <v>121486731</v>
       </c>
       <c r="B37" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4280,42 +4099,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499087</v>
+        <v>499150</v>
       </c>
       <c r="R37" t="n">
-        <v>6820462</v>
+        <v>6820595</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,7 +4167,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4375,19 +4185,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121486738</v>
+        <v>121486736</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4415,7 +4220,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499060</v>
+        <v>499040</v>
       </c>
       <c r="R38" t="n">
         <v>6820435</v>
@@ -4477,59 +4282,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121486628</v>
+        <v>121486737</v>
       </c>
       <c r="B39" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>499248</v>
+        <v>499047</v>
       </c>
       <c r="R39" t="n">
-        <v>6820414</v>
+        <v>6820437</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4564,18 +4355,12 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På bruten topp på kalhygge</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4594,19 +4379,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121486720</v>
+        <v>121486738</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4634,10 +4414,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>499064</v>
+        <v>499060</v>
       </c>
       <c r="R40" t="n">
-        <v>6820411</v>
+        <v>6820435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4696,19 +4476,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121486710</v>
+        <v>121486739</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4736,10 +4511,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>499134</v>
+        <v>499079</v>
       </c>
       <c r="R41" t="n">
-        <v>6820297</v>
+        <v>6820445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4798,19 +4573,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121486748</v>
+        <v>121486740</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4838,10 +4608,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>499224</v>
+        <v>499119</v>
       </c>
       <c r="R42" t="n">
-        <v>6820584</v>
+        <v>6820450</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4900,15 +4670,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121486649</v>
+        <v>121486742</v>
       </c>
       <c r="B43" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,42 +4681,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>499099</v>
+        <v>499140</v>
       </c>
       <c r="R43" t="n">
-        <v>6820449</v>
+        <v>6820485</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4992,7 +4749,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5011,19 +4767,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121486740</v>
+        <v>121486743</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5051,10 +4802,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>499119</v>
+        <v>499204</v>
       </c>
       <c r="R44" t="n">
-        <v>6820450</v>
+        <v>6820546</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5113,37 +4864,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121486623</v>
+        <v>121486744</v>
       </c>
       <c r="B45" t="n">
-        <v>79698</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5153,10 +4899,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>499112</v>
+        <v>499210</v>
       </c>
       <c r="R45" t="n">
-        <v>6820448</v>
+        <v>6820548</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,37 +4961,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121486586</v>
+        <v>121486745</v>
       </c>
       <c r="B46" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5255,10 +4996,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>499101</v>
+        <v>499219</v>
       </c>
       <c r="R46" t="n">
-        <v>6820489</v>
+        <v>6820563</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,37 +5058,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121486587</v>
+        <v>121486746</v>
       </c>
       <c r="B47" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5357,10 +5093,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>499137</v>
+        <v>499223</v>
       </c>
       <c r="R47" t="n">
-        <v>6820469</v>
+        <v>6820560</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5419,19 +5155,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121486718</v>
+        <v>121486747</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5459,10 +5190,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>499079</v>
+        <v>499236</v>
       </c>
       <c r="R48" t="n">
-        <v>6820344</v>
+        <v>6820567</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5521,37 +5252,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121486637</v>
+        <v>121486748</v>
       </c>
       <c r="B49" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5561,10 +5287,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>499221</v>
+        <v>499224</v>
       </c>
       <c r="R49" t="n">
-        <v>6820551</v>
+        <v>6820584</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5623,15 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121486646</v>
+        <v>121486749</v>
       </c>
       <c r="B50" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5639,42 +5360,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>499124</v>
+        <v>499243</v>
       </c>
       <c r="R50" t="n">
-        <v>6820580</v>
+        <v>6820625</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5715,7 +5428,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5734,37 +5446,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121486653</v>
+        <v>121486750</v>
       </c>
       <c r="B51" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5774,10 +5481,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>499063</v>
+        <v>499234</v>
       </c>
       <c r="R51" t="n">
-        <v>6820418</v>
+        <v>6820652</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5836,19 +5543,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121486713</v>
+        <v>121486751</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5876,10 +5578,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>499123</v>
+        <v>499226</v>
       </c>
       <c r="R52" t="n">
-        <v>6820323</v>
+        <v>6820660</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5938,15 +5640,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121475875</v>
+        <v>121486591</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5954,37 +5651,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långtallarna, Långtallarna, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>499095</v>
+        <v>499060</v>
       </c>
       <c r="R53" t="n">
-        <v>6820473</v>
+        <v>6820434</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6011,19 +5708,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6038,27 +5725,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121475595</v>
+        <v>121486592</v>
       </c>
       <c r="B54" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6066,37 +5748,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
+          <t>Djupdalsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>499216</v>
+        <v>499180</v>
       </c>
       <c r="R54" t="n">
-        <v>6820553</v>
+        <v>6820509</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6123,19 +5805,9 @@
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6150,15 +5822,3426 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121486593</v>
+      </c>
+      <c r="B55" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>499234</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6820652</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121486651</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>499244</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6820418</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121486652</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>499247</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6820414</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121486653</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>499063</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6820418</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121486654</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>499174</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6820509</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>121486658</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>499221</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6820551</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121486766</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>499091</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6820459</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>121488698</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hälsingland, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>499257</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6820637</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121486586</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>499101</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6820489</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121486587</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>499137</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6820469</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121486625</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>499245</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6820640</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>121475595</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>499216</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6820553</v>
+      </c>
+      <c r="S66" t="n">
+        <v>9</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>121475926</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>499261</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6820633</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt på stående och en liggande sälg.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>121486639</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>499291</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6820602</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121486640</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>499110</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6820446</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>121486641</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>499241</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6820619</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>121486642</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>499238</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6820665</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>121488286</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>499283</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6820577</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>121488695</v>
+      </c>
+      <c r="B73" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hälsingland, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>499253</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6820637</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>121486611</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>499075</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6820457</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>121486612</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>499163</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6820511</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>121486779</v>
+      </c>
+      <c r="B76" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>499036</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6820432</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>121486628</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>499248</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6820414</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På bruten topp på kalhygge</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121486629</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>499088</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6820469</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121486644</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>499088</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6820326</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121486645</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>499058</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6820539</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>121486646</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>499124</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6820580</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>121486647</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>499057</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6820438</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>121486648</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>499087</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6820462</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>121486649</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>499099</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6820449</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>121486626</v>
+      </c>
+      <c r="B85" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>499104</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6820567</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>121486635</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>499279</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6820470</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121486636</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>499244</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6820418</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121486637</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>499221</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6820551</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22554-2023 artfynd.xlsx
+++ b/artfynd/A 22554-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486643</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486622</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486623</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121488299</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121488306</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121475875</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486700</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486701</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486702</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486703</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486705</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486706</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486707</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2048,6 +2118,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486708</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486709</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486710</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486711</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486712</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486713</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2630,6 +2730,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486714</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486715</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2824,6 +2934,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486717</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2921,6 +3036,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486718</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3018,6 +3138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486719</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3115,6 +3240,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486720</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3212,6 +3342,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486721</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3309,6 +3444,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486722</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3406,6 +3546,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486723</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3503,6 +3648,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486724</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3600,6 +3750,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486725</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3697,6 +3852,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486726</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3794,6 +3954,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486727</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3891,6 +4056,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486728</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3988,6 +4158,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486729</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4085,6 +4260,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486730</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4182,6 +4362,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486731</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4279,6 +4464,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486736</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4376,6 +4566,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486737</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4473,6 +4668,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486738</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4570,6 +4770,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486739</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4667,6 +4872,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486740</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4764,6 +4974,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486742</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4861,6 +5076,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486743</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4958,6 +5178,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486744</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5055,6 +5280,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486745</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5152,6 +5382,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486746</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5249,6 +5484,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486747</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5346,6 +5586,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486748</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5443,6 +5688,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486749</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5540,6 +5790,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486750</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5637,6 +5892,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486751</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5734,6 +5994,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486591</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5831,6 +6096,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486592</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5928,6 +6198,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486593</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6025,6 +6300,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486651</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6122,6 +6402,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486652</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6219,6 +6504,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486653</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6316,6 +6606,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486654</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6413,6 +6708,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486658</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6510,6 +6810,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486766</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6607,6 +6912,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121488698</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6704,6 +7014,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486586</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6801,6 +7116,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486587</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6898,6 +7218,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486625</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7005,6 +7330,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121475595</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7117,6 +7447,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121475926</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7214,6 +7549,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486639</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7311,6 +7651,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486640</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7408,6 +7753,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486641</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7505,6 +7855,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486642</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7606,6 +7961,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121488286</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7703,6 +8063,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121488695</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7800,6 +8165,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486611</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7897,6 +8267,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486612</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7999,6 +8374,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486779</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8111,6 +8491,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486628</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8218,6 +8603,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486629</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8324,6 +8714,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486644</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8430,6 +8825,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486645</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8536,6 +8936,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486646</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8642,6 +9047,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486647</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8748,6 +9158,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486648</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8854,6 +9269,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486649</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8951,6 +9371,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486626</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9048,6 +9473,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486635</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9145,6 +9575,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486636</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9242,8 +9677,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121486637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>